--- a/output/Supplementary_Table_S1_Global_Synthesis.xlsx
+++ b/output/Supplementary_Table_S1_Global_Synthesis.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Adp-N &gt; N-Gen</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -490,10 +490,10 @@
         <v>4.3073</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0197</v>
+        <v>0.0172</v>
       </c>
       <c r="G2" t="n">
-        <v>99.54000000000001</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -504,7 +504,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>N-Adp &gt; Gen-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -521,10 +521,10 @@
         <v>3.3722</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0301</v>
+        <v>0.0455</v>
       </c>
       <c r="G3" t="n">
-        <v>99.11</v>
+        <v>98.65000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -535,7 +535,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SOV &amp; N-Gen &gt; N-Adj</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,10 +552,10 @@
         <v>4.7977</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0194</v>
+        <v>0.0179</v>
       </c>
       <c r="G4" t="n">
-        <v>99.59999999999999</v>
+        <v>99.63</v>
       </c>
     </row>
     <row r="5">
@@ -566,7 +566,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OV &gt; V-Mod</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -583,10 +583,10 @@
         <v>5.358</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1359</v>
+        <v>0.0257</v>
       </c>
       <c r="G5" t="n">
-        <v>97.45999999999999</v>
+        <v>99.52</v>
       </c>
     </row>
     <row r="6">
@@ -597,7 +597,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VSO &gt; Adp-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -614,10 +614,10 @@
         <v>4.6431</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5262</v>
+        <v>0.146</v>
       </c>
       <c r="G6" t="n">
-        <v>88.67</v>
+        <v>96.86</v>
       </c>
     </row>
     <row r="7">
@@ -628,7 +628,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VSO &gt; N-Adj</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -645,10 +645,10 @@
         <v>3.592</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4772</v>
+        <v>2.6432</v>
       </c>
       <c r="G7" t="n">
-        <v>86.72</v>
+        <v>26.41</v>
       </c>
     </row>
     <row r="8">
@@ -659,7 +659,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Adj-N &gt; Num-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -676,10 +676,10 @@
         <v>3.7188</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0571</v>
+        <v>0.0829</v>
       </c>
       <c r="G8" t="n">
-        <v>98.47</v>
+        <v>97.77</v>
       </c>
     </row>
     <row r="9">
@@ -690,7 +690,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rel-N &gt; Adj-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -707,10 +707,10 @@
         <v>3.2377</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0301</v>
+        <v>0.0325</v>
       </c>
       <c r="G9" t="n">
-        <v>99.06999999999999</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
@@ -721,7 +721,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VSO &amp; N-Adj &gt; N-Gen</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -738,10 +738,10 @@
         <v>4.3286</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2437</v>
+        <v>0.8068</v>
       </c>
       <c r="G10" t="n">
-        <v>94.37</v>
+        <v>81.36</v>
       </c>
     </row>
     <row r="11">
@@ -752,7 +752,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Adp-N &amp; no SVO &amp; N-Adj &gt; N-Gen</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -769,10 +769,10 @@
         <v>2.7683</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6025</v>
+        <v>2.1785</v>
       </c>
       <c r="G11" t="n">
-        <v>42.11</v>
+        <v>21.31</v>
       </c>
     </row>
     <row r="12">
@@ -783,7 +783,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Adp-N &amp; N-Dem &gt; N-Adj</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -800,10 +800,10 @@
         <v>4.1821</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0701</v>
+        <v>0.0354</v>
       </c>
       <c r="G12" t="n">
-        <v>98.31999999999999</v>
+        <v>99.15000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -814,7 +814,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Adp-N &amp; N-Num &gt; N-Adj</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -831,10 +831,10 @@
         <v>4.4397</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4775</v>
+        <v>1.8878</v>
       </c>
       <c r="G13" t="n">
-        <v>66.72</v>
+        <v>57.48</v>
       </c>
     </row>
     <row r="14">
@@ -845,7 +845,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Adp-N &amp; N-Adj &gt; N-Rel</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -862,21 +862,21 @@
         <v>3.9625</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0236</v>
+        <v>0.0242</v>
       </c>
       <c r="G14" t="n">
-        <v>99.40000000000001</v>
+        <v>99.39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0107CKA</t>
+          <t>0107AKA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VO &gt; N-Gen</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -890,24 +890,24 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4.8632</v>
+        <v>5.2508</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0206</v>
+        <v>0.0199</v>
       </c>
       <c r="G15" t="n">
-        <v>99.58</v>
+        <v>99.62</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0108KA</t>
+          <t>0107CKA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>OV &gt; Sent-Q</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -921,24 +921,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5.2151</v>
+        <v>4.8632</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0185</v>
+        <v>0.0186</v>
       </c>
       <c r="G16" t="n">
-        <v>99.64</v>
+        <v>99.62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0116KA</t>
+          <t>0108KA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>case &gt; number</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -952,24 +952,24 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2.3053</v>
+        <v>5.2151</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0413</v>
+        <v>0.023</v>
       </c>
       <c r="G17" t="n">
-        <v>98.20999999999999</v>
+        <v>99.56</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0121KA</t>
+          <t>0116KA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Adp-N &amp; N-Num &gt; N-Rel</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -983,24 +983,24 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4.3015</v>
+        <v>2.3053</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6001</v>
+        <v>0.0473</v>
       </c>
       <c r="G18" t="n">
-        <v>62.8</v>
+        <v>97.95</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0166KA</t>
+          <t>0121KA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>pref-V Obj &gt; V Agr Sbj</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1014,24 +1014,24 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3.6427</v>
+        <v>4.3015</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0554</v>
+        <v>0.3778</v>
       </c>
       <c r="G19" t="n">
-        <v>98.48</v>
+        <v>91.22</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0176KA</t>
+          <t>0147KA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>N-Gen &gt; N-Rel</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1045,24 +1045,24 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4.8968</v>
+        <v>1.609</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6637</v>
+        <v>0.0579</v>
       </c>
       <c r="G20" t="n">
-        <v>66.02</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0177KA</t>
+          <t>0166KA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>N-Adp &amp; Dem-N &gt; Gen-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1076,24 +1076,24 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3.0797</v>
+        <v>3.6427</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0377</v>
+        <v>0.0314</v>
       </c>
       <c r="G21" t="n">
-        <v>98.78</v>
+        <v>99.14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0179AKA</t>
+          <t>0176KA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>gender Adj &gt; number Adj</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1107,24 +1107,24 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3.502</v>
+        <v>4.8968</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0181</v>
+        <v>2.0709</v>
       </c>
       <c r="G22" t="n">
-        <v>99.48</v>
+        <v>57.71</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0230AKA</t>
+          <t>0177KA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>rigid order &gt; no case</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1138,24 +1138,24 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2.0356</v>
+        <v>3.0797</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0566</v>
+        <v>0.0362</v>
       </c>
       <c r="G23" t="n">
-        <v>97.22</v>
+        <v>98.81999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0230BKA</t>
+          <t>0179AKA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>no case &gt; Adp-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1169,24 +1169,24 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2.707</v>
+        <v>3.502</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0583</v>
+        <v>0.0384</v>
       </c>
       <c r="G24" t="n">
-        <v>97.84999999999999</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0230FKA</t>
+          <t>0179BKA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>free order &gt; no Adp-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1200,24 +1200,24 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.081</v>
+        <v>3.8542</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0557</v>
+        <v>1.4401</v>
       </c>
       <c r="G25" t="n">
-        <v>97.33</v>
+        <v>62.64</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0231BKA</t>
+          <t>0230AKA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>free order | case &gt; gradation adj inflect</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1231,24 +1231,24 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.8291</v>
+        <v>2.0356</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0919</v>
+        <v>0.1214</v>
       </c>
       <c r="G26" t="n">
-        <v>96.75</v>
+        <v>94.04000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0239CKA</t>
+          <t>0230BKA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>free order &gt; gender (pro)noun adj art</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1262,24 +1262,24 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.0907</v>
+        <v>2.707</v>
       </c>
       <c r="F27" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.0601</v>
       </c>
       <c r="G27" t="n">
-        <v>96.26000000000001</v>
+        <v>97.78</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0240AKA</t>
+          <t>0230EKA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ergative case &gt; Gen-N &amp; N-Adj</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1293,24 +1293,24 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4.8242</v>
+        <v>3.1869</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0496</v>
+        <v>0.0266</v>
       </c>
       <c r="G28" t="n">
-        <v>98.97</v>
+        <v>99.17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0332KA</t>
+          <t>0230FKA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>o suffix &gt; s suffix</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1324,24 +1324,24 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3.5825</v>
+        <v>2.081</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0274</v>
+        <v>0.068</v>
       </c>
       <c r="G29" t="n">
-        <v>99.23999999999999</v>
+        <v>96.73</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0356KA</t>
+          <t>0231BKA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>verb agree S&amp;P suffixal &gt; SV</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1355,24 +1355,24 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4.3424</v>
+        <v>2.8291</v>
       </c>
       <c r="F30" t="n">
-        <v>2.1896</v>
+        <v>0.0569</v>
       </c>
       <c r="G30" t="n">
-        <v>49.58</v>
+        <v>97.98999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0365KA</t>
+          <t>0239CKA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>verb agree S &amp; prefixal verb agree P &gt; SV</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1386,24 +1386,24 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4.4737</v>
+        <v>2.0907</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1762</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>96.06</v>
+        <v>96.34999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0386KA</t>
+          <t>0240AKA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nominal inflection &gt; verbal inflection</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1417,24 +1417,24 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2.3485</v>
+        <v>4.8242</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0399</v>
+        <v>0.1558</v>
       </c>
       <c r="G32" t="n">
-        <v>98.3</v>
+        <v>96.77</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0446KA</t>
+          <t>0247KA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>V-final | free &gt; N-Adp | case</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1448,24 +1448,24 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2.566</v>
+        <v>3.4121</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0308</v>
+        <v>0.0317</v>
       </c>
       <c r="G33" t="n">
-        <v>98.8</v>
+        <v>99.06999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0493BKA</t>
+          <t>0332KA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sent-Q &gt; N-Adp</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1479,24 +1479,24 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1.9639</v>
+        <v>3.5825</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0524</v>
+        <v>0.0248</v>
       </c>
       <c r="G34" t="n">
-        <v>97.33</v>
+        <v>99.31</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0506KA</t>
+          <t>0356KA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>inflection &gt; word formation</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1510,24 +1510,24 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1.864</v>
+        <v>4.3424</v>
       </c>
       <c r="F35" t="n">
-        <v>1.4886</v>
+        <v>1.9695</v>
       </c>
       <c r="G35" t="n">
-        <v>20.14</v>
+        <v>54.65</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0507KA</t>
+          <t>0365KA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>(person)-number (verb) &gt; tense-mood (verb)</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1541,24 +1541,24 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3.6421</v>
+        <v>4.4737</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0335</v>
+        <v>0.0578</v>
       </c>
       <c r="G36" t="n">
-        <v>99.08</v>
+        <v>98.70999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0569KA</t>
+          <t>0386KA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>no case (noun) &gt; article</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1572,24 +1572,24 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3.2784</v>
+        <v>2.3485</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0304</v>
+        <v>0.041</v>
       </c>
       <c r="G37" t="n">
-        <v>99.06999999999999</v>
+        <v>98.25</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0577KA</t>
+          <t>0446KA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>suppl noun &gt; suppl pron|verb</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1603,24 +1603,24 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2.1474</v>
+        <v>2.566</v>
       </c>
       <c r="F38" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.0344</v>
       </c>
       <c r="G38" t="n">
-        <v>96.45</v>
+        <v>98.66</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0582KA</t>
+          <t>0493BKA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>inflection (noun) &gt; inflection (pronoun)</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1634,24 +1634,24 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2.6821</v>
+        <v>1.9639</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0658</v>
+        <v>0.0469</v>
       </c>
       <c r="G39" t="n">
-        <v>97.55</v>
+        <v>97.61</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0668KA</t>
+          <t>0506KA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SOV &gt; Sent-Q</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1665,24 +1665,24 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5.4762</v>
+        <v>1.864</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0171</v>
+        <v>3.888</v>
       </c>
       <c r="G40" t="n">
-        <v>99.69</v>
+        <v>-108.59</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0822KA</t>
+          <t>0507KA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>correlative Rel &gt; V-final;</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1696,24 +1696,24 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1.3651</v>
+        <v>3.6421</v>
       </c>
       <c r="F41" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0328</v>
       </c>
       <c r="G41" t="n">
-        <v>94.72</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0889BKA</t>
+          <t>0569KA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VO &gt; prefixes</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1727,24 +1727,24 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5.3508</v>
+        <v>3.2784</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0175</v>
+        <v>0.0312</v>
       </c>
       <c r="G42" t="n">
-        <v>99.67</v>
+        <v>99.05</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0917AKA</t>
+          <t>0577KA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VO &gt; Qpart-S</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1758,24 +1758,24 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5.6748</v>
+        <v>2.1474</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0187</v>
+        <v>0.0418</v>
       </c>
       <c r="G43" t="n">
-        <v>99.67</v>
+        <v>98.05</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0917BKA</t>
+          <t>0582KA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OV &gt; Gen-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1789,24 +1789,24 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5.2069</v>
+        <v>2.6821</v>
       </c>
       <c r="F44" t="n">
-        <v>0.053</v>
+        <v>0.0517</v>
       </c>
       <c r="G44" t="n">
-        <v>98.98</v>
+        <v>98.06999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0964AKA</t>
+          <t>0668KA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VO &gt; Art-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1820,24 +1820,24 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5.5171</v>
+        <v>5.4762</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0258</v>
+        <v>0.0163</v>
       </c>
       <c r="G45" t="n">
-        <v>99.53</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0982KA</t>
+          <t>0822KA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>locative comparative &gt; SOV | VSO</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1851,24 +1851,24 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2.4174</v>
+        <v>1.3651</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0601</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>97.51000000000001</v>
+        <v>94.95</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0983KA</t>
+          <t>0889BKA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>exceed comparative &gt; SVO</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1882,24 +1882,24 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1.5931</v>
+        <v>5.3508</v>
       </c>
       <c r="F47" t="n">
-        <v>0.041</v>
+        <v>0.0169</v>
       </c>
       <c r="G47" t="n">
-        <v>97.43000000000001</v>
+        <v>99.68000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1027AKA</t>
+          <t>0917AKA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VO -&gt; no morph tense | no  case</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1913,24 +1913,24 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4.9982</v>
+        <v>5.6748</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0196</v>
+        <v>0.0192</v>
       </c>
       <c r="G48" t="n">
-        <v>99.61</v>
+        <v>99.66</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1027BKA</t>
+          <t>0917BKA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>no morph tense -&gt; no case|VO</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1944,24 +1944,24 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3.1951</v>
+        <v>5.2069</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0311</v>
+        <v>0.0267</v>
       </c>
       <c r="G49" t="n">
-        <v>99.03</v>
+        <v>99.48999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1028BKA</t>
+          <t>0964AKA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>morph tense &gt; case | OV</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1975,24 +1975,24 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3.363</v>
+        <v>5.5171</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0272</v>
+        <v>0.0184</v>
       </c>
       <c r="G50" t="n">
-        <v>99.19</v>
+        <v>99.67</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1114KA</t>
+          <t>0982KA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>VO &gt; Comp-S</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2006,24 +2006,24 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4.5168</v>
+        <v>2.4174</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0164</v>
+        <v>0.0558</v>
       </c>
       <c r="G51" t="n">
-        <v>99.64</v>
+        <v>97.69</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1142AKA</t>
+          <t>0983KA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>passive &gt; SVO</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2037,24 +2037,24 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3.6563</v>
+        <v>1.5931</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0256</v>
+        <v>0.0443</v>
       </c>
       <c r="G52" t="n">
-        <v>99.3</v>
+        <v>97.22</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1163KA</t>
+          <t>1027AKA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>indefinite article &gt; definite article</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2068,24 +2068,24 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1.2682</v>
+        <v>4.9982</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0624</v>
+        <v>0.0195</v>
       </c>
       <c r="G53" t="n">
-        <v>95.08</v>
+        <v>99.61</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1216KA</t>
+          <t>1027BKA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>N-Adp &gt; case (noun)</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2099,24 +2099,24 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3.9312</v>
+        <v>3.1951</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0231</v>
+        <v>0.033</v>
       </c>
       <c r="G54" t="n">
-        <v>99.41</v>
+        <v>98.97</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1372KA</t>
+          <t>1028BKA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>verb HAVE &gt; SVO</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2130,24 +2130,24 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3.3415</v>
+        <v>3.363</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0544</v>
+        <v>0.0294</v>
       </c>
       <c r="G55" t="n">
-        <v>98.37</v>
+        <v>99.13</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1415KA</t>
+          <t>1114KA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>poss agree &gt; verbal agree S</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2161,24 +2161,24 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3.471</v>
+        <v>4.5168</v>
       </c>
       <c r="F56" t="n">
-        <v>0.039</v>
+        <v>0.016</v>
       </c>
       <c r="G56" t="n">
-        <v>98.88</v>
+        <v>99.65000000000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1427KA</t>
+          <t>1142AKA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>no prefix &gt; infl local cases</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2192,24 +2192,24 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4.0676</v>
+        <v>3.6563</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0375</v>
+        <v>0.0259</v>
       </c>
       <c r="G57" t="n">
-        <v>99.08</v>
+        <v>99.29000000000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1430KA</t>
+          <t>1163KA</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>N-poss suf &gt; no PRS overt copula “to be”</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3.3706</v>
+        <v>1.2682</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0388</v>
+        <v>0.0613</v>
       </c>
       <c r="G58" t="n">
-        <v>98.84999999999999</v>
+        <v>95.17</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1431NKA</t>
+          <t>1216KA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>more case &gt; less tense</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2254,24 +2254,24 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3.067</v>
+        <v>3.9312</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0536</v>
+        <v>0.0238</v>
       </c>
       <c r="G59" t="n">
-        <v>98.25</v>
+        <v>99.39</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1499KA</t>
+          <t>1334AKA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SVC &gt; little inflection</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2285,24 +2285,24 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2.2427</v>
+        <v>1.786</v>
       </c>
       <c r="F60" t="n">
-        <v>0.0621</v>
+        <v>0.0941</v>
       </c>
       <c r="G60" t="n">
-        <v>97.23</v>
+        <v>94.73</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1531KA</t>
+          <t>1372KA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>V-initial &gt; prefixes</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2316,24 +2316,24 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5.8722</v>
+        <v>3.3415</v>
       </c>
       <c r="F61" t="n">
-        <v>0.3678</v>
+        <v>0.0463</v>
       </c>
       <c r="G61" t="n">
-        <v>93.73999999999999</v>
+        <v>98.61</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1537KA</t>
+          <t>1415KA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>V-initial &gt; C-Sent</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2347,24 +2347,24 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5.4787</v>
+        <v>3.471</v>
       </c>
       <c r="F62" t="n">
-        <v>0.2365</v>
+        <v>0.0403</v>
       </c>
       <c r="G62" t="n">
-        <v>95.68000000000001</v>
+        <v>98.84</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1544KA</t>
+          <t>1427KA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>V-initial &gt; verbal case-marking</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2378,24 +2378,24 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5.8409</v>
+        <v>4.0676</v>
       </c>
       <c r="F63" t="n">
-        <v>1.0991</v>
+        <v>1.5818</v>
       </c>
       <c r="G63" t="n">
-        <v>81.18000000000001</v>
+        <v>61.11</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1545KA</t>
+          <t>1430KA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>V-initial &gt; N-Dem-Num-Adj</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2409,24 +2409,24 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5.7574</v>
+        <v>3.3706</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1635</v>
+        <v>0.029</v>
       </c>
       <c r="G64" t="n">
-        <v>97.16</v>
+        <v>99.14</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1559KA</t>
+          <t>1431NKA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>V-initial &gt; passive voice</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2440,24 +2440,24 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5.6687</v>
+        <v>3.067</v>
       </c>
       <c r="F65" t="n">
-        <v>1.3031</v>
+        <v>0.0297</v>
       </c>
       <c r="G65" t="n">
-        <v>77.01000000000001</v>
+        <v>99.03</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1589KA</t>
+          <t>1499KA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>V-final &gt; postposing &amp; suffixes</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2471,24 +2471,24 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4.9031</v>
+        <v>2.2427</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0165</v>
+        <v>0.0521</v>
       </c>
       <c r="G66" t="n">
-        <v>99.66</v>
+        <v>97.68000000000001</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1593KA</t>
+          <t>1531KA</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>internal relative clause &gt; null anaphora</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2502,24 +2502,24 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1.9558</v>
+        <v>5.8722</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0505</v>
+        <v>0.1454</v>
       </c>
       <c r="G67" t="n">
-        <v>97.42</v>
+        <v>97.52</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1610KA</t>
+          <t>1537KA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>verb-patient agreement &gt; V-initial | V-final</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2533,24 +2533,24 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4.2533</v>
+        <v>5.4787</v>
       </c>
       <c r="F68" t="n">
-        <v>0.207</v>
+        <v>0.0741</v>
       </c>
       <c r="G68" t="n">
-        <v>95.13</v>
+        <v>98.65000000000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1611KA</t>
+          <t>1544KA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>verb-patient agreement &gt; verb-agent agreement</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2564,24 +2564,24 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3.5488</v>
+        <v>5.8409</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0678</v>
+        <v>0.1836</v>
       </c>
       <c r="G69" t="n">
-        <v>98.09</v>
+        <v>96.86</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1621KA</t>
+          <t>1545KA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Adj &gt; no sortal classifiers</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2595,24 +2595,24 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1.2332</v>
+        <v>5.7574</v>
       </c>
       <c r="F70" t="n">
-        <v>0.3079</v>
+        <v>0.23</v>
       </c>
       <c r="G70" t="n">
-        <v>75.03</v>
+        <v>96</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1741KA</t>
+          <t>1559KA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Gen prefix &gt; verbal prefixes</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2626,24 +2626,24 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3.1169</v>
+        <v>5.6687</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0393</v>
+        <v>0.2846</v>
       </c>
       <c r="G71" t="n">
-        <v>98.73999999999999</v>
+        <v>94.98</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1994CKA</t>
+          <t>1589KA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>non-affixed Gen-N &gt; verbal prefixes pers um</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2657,24 +2657,24 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3.722</v>
+        <v>4.9031</v>
       </c>
       <c r="F72" t="n">
-        <v>0.0241</v>
+        <v>0.0158</v>
       </c>
       <c r="G72" t="n">
-        <v>99.34999999999999</v>
+        <v>99.68000000000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2012KA</t>
+          <t>1593KA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>switch-reference marking &gt; accusitive</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2688,199 +2688,199 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2.6491</v>
+        <v>1.9558</v>
       </c>
       <c r="F73" t="n">
-        <v>0.5505</v>
+        <v>0.0664</v>
       </c>
       <c r="G73" t="n">
-        <v>79.22</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0107AKA</t>
+          <t>1610KA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>VO &gt; N-Rel</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Polar Distortion Artifacts</t>
+          <t>Consensus Non-Significant</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Significant (2D Only)</t>
+          <t>Non-Significant</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5.2508</v>
+        <v>4.2533</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0203</v>
+        <v>0.0445</v>
       </c>
       <c r="G74" t="n">
-        <v>99.61</v>
+        <v>98.95</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0147KA</t>
+          <t>1611KA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>V-like Attr Adj &gt; SVO</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Polar Distortion Artifacts</t>
+          <t>Consensus Non-Significant</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Significant (2D Only)</t>
+          <t>Non-Significant</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1.609</v>
+        <v>3.5488</v>
       </c>
       <c r="F75" t="n">
-        <v>0.1169</v>
+        <v>0.025</v>
       </c>
       <c r="G75" t="n">
-        <v>92.73</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0179BKA</t>
+          <t>1621KA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>gender Dem &gt; number Dem</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Polar Distortion Artifacts</t>
+          <t>Consensus Non-Significant</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Significant (2D Only)</t>
+          <t>Non-Significant</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3.8542</v>
+        <v>1.2332</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0162</v>
+        <v>0.1768</v>
       </c>
       <c r="G76" t="n">
-        <v>99.58</v>
+        <v>85.66</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0230EKA</t>
+          <t>1741KA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>case &gt; no Adp-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Polar Distortion Artifacts</t>
+          <t>Consensus Non-Significant</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Significant (2D Only)</t>
+          <t>Non-Significant</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3.1869</v>
+        <v>3.1169</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0258</v>
+        <v>0.036</v>
       </c>
       <c r="G77" t="n">
-        <v>99.19</v>
+        <v>98.84</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0247KA</t>
+          <t>1994CKA</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>accusative &gt; gender</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Polar Distortion Artifacts</t>
+          <t>Consensus Non-Significant</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Significant (2D Only)</t>
+          <t>Non-Significant</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3.4121</v>
+        <v>3.722</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0533</v>
+        <v>0.0311</v>
       </c>
       <c r="G78" t="n">
-        <v>98.44</v>
+        <v>99.16</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1334AKA</t>
+          <t>2012KA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Adp-N &amp; Rel-N &gt; Gen-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Polar Distortion Artifacts</t>
+          <t>Consensus Non-Significant</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Significant (2D Only)</t>
+          <t>Non-Significant</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1.786</v>
+        <v>2.6491</v>
       </c>
       <c r="F79" t="n">
-        <v>0.0335</v>
+        <v>0.0992</v>
       </c>
       <c r="G79" t="n">
-        <v>98.12</v>
+        <v>96.25</v>
       </c>
     </row>
     <row r="80">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>VO &gt; Mod-V</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2908,10 +2908,10 @@
         <v>5.3779</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0198</v>
+        <v>0.0191</v>
       </c>
       <c r="G80" t="n">
-        <v>99.63</v>
+        <v>99.64</v>
       </c>
     </row>
     <row r="81">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Adj-N &gt; Dem-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2939,10 +2939,10 @@
         <v>3.8289</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0281</v>
+        <v>0.0245</v>
       </c>
       <c r="G81" t="n">
-        <v>99.27</v>
+        <v>99.36</v>
       </c>
     </row>
     <row r="82">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Rel-N &gt; N-Adp</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2970,10 +2970,10 @@
         <v>3.1413</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0359</v>
+        <v>0.0368</v>
       </c>
       <c r="G82" t="n">
-        <v>98.86</v>
+        <v>98.83</v>
       </c>
     </row>
     <row r="83">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SOV &amp; Adj-N &gt; Gen-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3001,10 +3001,10 @@
         <v>4.865</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0178</v>
+        <v>0.0202</v>
       </c>
       <c r="G83" t="n">
-        <v>99.63</v>
+        <v>99.59</v>
       </c>
     </row>
     <row r="84">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>N-Adp &amp; (Adj-N | Rel-N) &gt; PossPron-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3032,10 +3032,10 @@
         <v>3.2227</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0314</v>
+        <v>0.0309</v>
       </c>
       <c r="G84" t="n">
-        <v>99.02</v>
+        <v>99.04000000000001</v>
       </c>
     </row>
     <row r="85">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>N-Gen &gt; N-Adj</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3063,10 +3063,10 @@
         <v>4.7382</v>
       </c>
       <c r="F85" t="n">
-        <v>0.1361</v>
+        <v>0.0342</v>
       </c>
       <c r="G85" t="n">
-        <v>97.13</v>
+        <v>99.28</v>
       </c>
     </row>
     <row r="86">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Adp-N &amp; N-Dem &gt; N-Gen</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3094,10 +3094,10 @@
         <v>3.417</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0368</v>
+        <v>0.0302</v>
       </c>
       <c r="G86" t="n">
-        <v>98.92</v>
+        <v>99.12</v>
       </c>
     </row>
     <row r="87">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Adp-N &amp; N-Num &gt; N-Gen</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3125,10 +3125,10 @@
         <v>4.0499</v>
       </c>
       <c r="F87" t="n">
-        <v>0.0561</v>
+        <v>0.3563</v>
       </c>
       <c r="G87" t="n">
-        <v>98.61</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="88">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Adp-N &amp; N-Gen &gt; N-Rel</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3156,10 +3156,10 @@
         <v>5.1177</v>
       </c>
       <c r="F88" t="n">
-        <v>0.2904</v>
+        <v>0.5793</v>
       </c>
       <c r="G88" t="n">
-        <v>94.33</v>
+        <v>88.68000000000001</v>
       </c>
     </row>
     <row r="89">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>N-Adp &amp; Num-N &gt; Gen-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3187,10 +3187,10 @@
         <v>3.7005</v>
       </c>
       <c r="F89" t="n">
-        <v>0.0249</v>
+        <v>0.0253</v>
       </c>
       <c r="G89" t="n">
-        <v>99.33</v>
+        <v>99.31999999999999</v>
       </c>
     </row>
     <row r="90">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>case Nouns &gt; case PronN</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3218,10 +3218,10 @@
         <v>2.9806</v>
       </c>
       <c r="F90" t="n">
-        <v>0.0367</v>
+        <v>0.0457</v>
       </c>
       <c r="G90" t="n">
-        <v>98.77</v>
+        <v>98.47</v>
       </c>
     </row>
     <row r="91">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nominal case &gt; verbal inflection</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3249,10 +3249,10 @@
         <v>3.1125</v>
       </c>
       <c r="F91" t="n">
-        <v>0.0338</v>
+        <v>0.0275</v>
       </c>
       <c r="G91" t="n">
-        <v>98.91</v>
+        <v>99.12</v>
       </c>
     </row>
     <row r="92">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nominal number &gt; nominal case</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3280,10 +3280,10 @@
         <v>2.2466</v>
       </c>
       <c r="F92" t="n">
-        <v>0.0456</v>
+        <v>0.0412</v>
       </c>
       <c r="G92" t="n">
-        <v>97.97</v>
+        <v>98.17</v>
       </c>
     </row>
     <row r="93">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>rigid order &gt; Adp-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3311,10 +3311,10 @@
         <v>2.0821</v>
       </c>
       <c r="F93" t="n">
-        <v>0.0557</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="G93" t="n">
-        <v>97.33</v>
+        <v>96.54000000000001</v>
       </c>
     </row>
     <row r="94">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>free order &gt; case</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3342,10 +3342,10 @@
         <v>2.0464</v>
       </c>
       <c r="F94" t="n">
-        <v>0.0566</v>
+        <v>0.1251</v>
       </c>
       <c r="G94" t="n">
-        <v>97.23999999999999</v>
+        <v>93.89</v>
       </c>
     </row>
     <row r="95">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>rigid order | no case &gt; gradation adj  function word</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3373,10 +3373,10 @@
         <v>2.7331</v>
       </c>
       <c r="F95" t="n">
-        <v>0.048</v>
+        <v>0.0528</v>
       </c>
       <c r="G95" t="n">
-        <v>98.23999999999999</v>
+        <v>98.06999999999999</v>
       </c>
     </row>
     <row r="96">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>number Adj &gt; number noun</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3404,7 +3404,7 @@
         <v>2.1665</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0354</v>
+        <v>0.0356</v>
       </c>
       <c r="G96" t="n">
         <v>98.36</v>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>rigid order &gt; N-Rel</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3435,10 +3435,10 @@
         <v>1.7659</v>
       </c>
       <c r="F97" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.1051</v>
       </c>
       <c r="G97" t="n">
-        <v>94.66</v>
+        <v>94.05</v>
       </c>
     </row>
     <row r="98">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>free order &gt;  case noun|pronoun</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3466,10 +3466,10 @@
         <v>2.0996</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0619</v>
+        <v>0.0796</v>
       </c>
       <c r="G98" t="n">
-        <v>97.05</v>
+        <v>96.20999999999999</v>
       </c>
     </row>
     <row r="99">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>free order &gt; number noun adj art</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3497,10 +3497,10 @@
         <v>1.834</v>
       </c>
       <c r="F99" t="n">
-        <v>0.047</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="G99" t="n">
-        <v>97.43000000000001</v>
+        <v>96.42</v>
       </c>
     </row>
     <row r="100">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>free order &gt; inflection nouns</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3528,10 +3528,10 @@
         <v>1.894</v>
       </c>
       <c r="F100" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="G100" t="n">
-        <v>96.53</v>
+        <v>96.83</v>
       </c>
     </row>
     <row r="101">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>rigid order &amp; no inversion &gt; no inflection nouns</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3559,10 +3559,10 @@
         <v>0.9199000000000001</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0584</v>
+        <v>0.0548</v>
       </c>
       <c r="G101" t="n">
-        <v>93.66</v>
+        <v>94.04000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ergative &gt; prefixal personal conjugation</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3590,10 +3590,10 @@
         <v>4.7484</v>
       </c>
       <c r="F102" t="n">
-        <v>0.0293</v>
+        <v>0.1094</v>
       </c>
       <c r="G102" t="n">
-        <v>99.38</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="103">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>number (adjective | verb) &gt; number (noun)</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3621,10 +3621,10 @@
         <v>2.1666</v>
       </c>
       <c r="F103" t="n">
-        <v>0.0357</v>
+        <v>0.0362</v>
       </c>
       <c r="G103" t="n">
-        <v>98.34999999999999</v>
+        <v>98.33</v>
       </c>
     </row>
     <row r="104">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>verb agr S prefix &gt; verb agr P</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3652,10 +3652,10 @@
         <v>4.0832</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0688</v>
+        <v>0.0155</v>
       </c>
       <c r="G104" t="n">
-        <v>98.31999999999999</v>
+        <v>99.62</v>
       </c>
     </row>
     <row r="105">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>s prefix &gt; o prefix | o suffix (weak)</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3683,10 +3683,10 @@
         <v>3.9487</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0178</v>
+        <v>0.032</v>
       </c>
       <c r="G105" t="n">
-        <v>99.55</v>
+        <v>99.19</v>
       </c>
     </row>
     <row r="106">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Adp-N &amp; no SOV &gt; N-Rel</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3714,10 +3714,10 @@
         <v>5.5622</v>
       </c>
       <c r="F106" t="n">
-        <v>0.0205</v>
+        <v>0.0199</v>
       </c>
       <c r="G106" t="n">
-        <v>99.63</v>
+        <v>99.64</v>
       </c>
     </row>
     <row r="107">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>non-accusative alignment &gt; V-initial</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3745,10 +3745,10 @@
         <v>3.8434</v>
       </c>
       <c r="F107" t="n">
-        <v>0.4363</v>
+        <v>0.4005</v>
       </c>
       <c r="G107" t="n">
-        <v>88.65000000000001</v>
+        <v>89.58</v>
       </c>
     </row>
     <row r="108">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>prefixes &gt; Adp-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3776,10 +3776,10 @@
         <v>1.8091</v>
       </c>
       <c r="F108" t="n">
-        <v>1.728</v>
+        <v>3.7493</v>
       </c>
       <c r="G108" t="n">
-        <v>4.48</v>
+        <v>-107.25</v>
       </c>
     </row>
     <row r="109">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>suffixes &gt; N-Adp</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3807,10 +3807,10 @@
         <v>4.01</v>
       </c>
       <c r="F109" t="n">
-        <v>0.4175</v>
+        <v>0.0413</v>
       </c>
       <c r="G109" t="n">
-        <v>89.59</v>
+        <v>98.97</v>
       </c>
     </row>
     <row r="110">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>obli (in)Def marking &gt; no obli numeral classifier</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3838,10 +3838,10 @@
         <v>2.5601</v>
       </c>
       <c r="F110" t="n">
-        <v>0.0485</v>
+        <v>0.0598</v>
       </c>
       <c r="G110" t="n">
-        <v>98.09999999999999</v>
+        <v>97.66</v>
       </c>
     </row>
     <row r="111">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>switch-reference marking &gt; V-final</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3869,10 +3869,10 @@
         <v>2.4176</v>
       </c>
       <c r="F111" t="n">
-        <v>0.0291</v>
+        <v>0.0252</v>
       </c>
       <c r="G111" t="n">
-        <v>98.8</v>
+        <v>98.95999999999999</v>
       </c>
     </row>
     <row r="112">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>OV &gt; suffixes</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3900,10 +3900,10 @@
         <v>5.6372</v>
       </c>
       <c r="F112" t="n">
-        <v>0.021</v>
+        <v>0.0203</v>
       </c>
       <c r="G112" t="n">
-        <v>99.63</v>
+        <v>99.64</v>
       </c>
     </row>
     <row r="113">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>OV &gt; Rel-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3931,10 +3931,10 @@
         <v>5.1719</v>
       </c>
       <c r="F113" t="n">
-        <v>0.0713</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="G113" t="n">
-        <v>98.62</v>
+        <v>98.20999999999999</v>
       </c>
     </row>
     <row r="114">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>OV &gt; N-Art</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3962,10 +3962,10 @@
         <v>5.3598</v>
       </c>
       <c r="F114" t="n">
-        <v>0.0405</v>
+        <v>0.023</v>
       </c>
       <c r="G114" t="n">
-        <v>99.23999999999999</v>
+        <v>99.56999999999999</v>
       </c>
     </row>
     <row r="115">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>agreement determiners &gt; agreement modifiers</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3993,10 +3993,10 @@
         <v>1.745</v>
       </c>
       <c r="F115" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="G115" t="n">
-        <v>95.95999999999999</v>
+        <v>96.15000000000001</v>
       </c>
     </row>
     <row r="116">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Rel-N &gt; N-Rel</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4024,10 +4024,10 @@
         <v>2.5423</v>
       </c>
       <c r="F116" t="n">
-        <v>0.0457</v>
+        <v>0.0439</v>
       </c>
       <c r="G116" t="n">
-        <v>98.2</v>
+        <v>98.27</v>
       </c>
     </row>
     <row r="117">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Adp-N &amp; Rel-N &amp; Gen-N &gt; Adj-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4055,10 +4055,10 @@
         <v>4.8257</v>
       </c>
       <c r="F117" t="n">
-        <v>8.8317</v>
+        <v>0.263</v>
       </c>
       <c r="G117" t="n">
-        <v>-83.01000000000001</v>
+        <v>94.55</v>
       </c>
     </row>
     <row r="118">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Adp-N &amp; Rel-N &amp; Gen-N &amp; Adj-N &gt; Dem-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4086,10 +4086,10 @@
         <v>3.3497</v>
       </c>
       <c r="F118" t="n">
-        <v>0.4403</v>
+        <v>0.5026</v>
       </c>
       <c r="G118" t="n">
-        <v>86.84999999999999</v>
+        <v>85</v>
       </c>
     </row>
     <row r="119">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>less case &gt; more tense</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4117,10 +4117,10 @@
         <v>2.9014</v>
       </c>
       <c r="F119" t="n">
-        <v>0.0453</v>
+        <v>0.0441</v>
       </c>
       <c r="G119" t="n">
-        <v>98.44</v>
+        <v>98.48</v>
       </c>
     </row>
     <row r="120">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>V-initial &gt; Q-Sent</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4148,10 +4148,10 @@
         <v>6.1396</v>
       </c>
       <c r="F120" t="n">
-        <v>2.6947</v>
+        <v>0.3314</v>
       </c>
       <c r="G120" t="n">
-        <v>56.11</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
     <row r="121">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>V-final &gt; more Adj-N agreement</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4179,10 +4179,10 @@
         <v>5.3949</v>
       </c>
       <c r="F121" t="n">
-        <v>0.0165</v>
+        <v>0.0185</v>
       </c>
       <c r="G121" t="n">
-        <v>99.69</v>
+        <v>99.66</v>
       </c>
     </row>
     <row r="122">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>V-initial &gt; less Adj-N agreement</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4210,10 +4210,10 @@
         <v>6.6938</v>
       </c>
       <c r="F122" t="n">
-        <v>1.0636</v>
+        <v>0.4802</v>
       </c>
       <c r="G122" t="n">
-        <v>84.11</v>
+        <v>92.83</v>
       </c>
     </row>
     <row r="123">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>V-initial &gt; no verb agreement | agreement 2 NPs</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4241,10 +4241,10 @@
         <v>5.9305</v>
       </c>
       <c r="F123" t="n">
-        <v>0.0665</v>
+        <v>2.0066</v>
       </c>
       <c r="G123" t="n">
-        <v>98.88</v>
+        <v>66.16</v>
       </c>
     </row>
     <row r="124">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>V-initial &gt; no overt copula</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4272,10 +4272,10 @@
         <v>6.0198</v>
       </c>
       <c r="F124" t="n">
-        <v>1.3725</v>
+        <v>1.1105</v>
       </c>
       <c r="G124" t="n">
-        <v>77.2</v>
+        <v>81.55</v>
       </c>
     </row>
     <row r="125">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>poss head-marked &gt; opp alien-inalien poss</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4303,10 +4303,10 @@
         <v>3.5375</v>
       </c>
       <c r="F125" t="n">
-        <v>0.0361</v>
+        <v>0.0325</v>
       </c>
       <c r="G125" t="n">
-        <v>98.98</v>
+        <v>99.08</v>
       </c>
     </row>
     <row r="126">
@@ -4317,7 +4317,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>internal relative clause &gt; SOV</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4334,10 +4334,10 @@
         <v>1.1324</v>
       </c>
       <c r="F126" t="n">
-        <v>0.0858</v>
+        <v>0.101</v>
       </c>
       <c r="G126" t="n">
-        <v>92.42</v>
+        <v>91.08</v>
       </c>
     </row>
     <row r="127">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>internal relative clause &gt; left-branching NP structure</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4365,10 +4365,10 @@
         <v>1.3654</v>
       </c>
       <c r="F127" t="n">
-        <v>0.1309</v>
+        <v>0.0452</v>
       </c>
       <c r="G127" t="n">
-        <v>90.41</v>
+        <v>96.69</v>
       </c>
     </row>
     <row r="128">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SOV &amp; N-Num &gt; N-Num agr</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4396,10 +4396,10 @@
         <v>4.4998</v>
       </c>
       <c r="F128" t="n">
-        <v>0.4971</v>
+        <v>0.8339</v>
       </c>
       <c r="G128" t="n">
-        <v>88.95</v>
+        <v>81.47</v>
       </c>
     </row>
     <row r="129">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SOV &amp; N-Dem &gt; N-Dem agr</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4427,10 +4427,10 @@
         <v>3.332</v>
       </c>
       <c r="F129" t="n">
-        <v>0.0849</v>
+        <v>0.1745</v>
       </c>
       <c r="G129" t="n">
-        <v>97.45</v>
+        <v>94.76000000000001</v>
       </c>
     </row>
     <row r="130">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Comp-S &gt; VSO</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4458,10 +4458,10 @@
         <v>2.4502</v>
       </c>
       <c r="F130" t="n">
-        <v>0.0313</v>
+        <v>0.0333</v>
       </c>
       <c r="G130" t="n">
-        <v>98.72</v>
+        <v>98.64</v>
       </c>
     </row>
     <row r="131">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>non-affixed Gen-N &gt; N-Adp</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4489,10 +4489,10 @@
         <v>3.6364</v>
       </c>
       <c r="F131" t="n">
-        <v>0.073</v>
+        <v>0.0266</v>
       </c>
       <c r="G131" t="n">
-        <v>97.98999999999999</v>
+        <v>99.27</v>
       </c>
     </row>
     <row r="132">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>non-affixed Gen-N &gt; Adj-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4520,10 +4520,10 @@
         <v>3.5193</v>
       </c>
       <c r="F132" t="n">
-        <v>0.0356</v>
+        <v>0.0315</v>
       </c>
       <c r="G132" t="n">
-        <v>98.98999999999999</v>
+        <v>99.11</v>
       </c>
     </row>
     <row r="133">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SOV|OSV &gt; case</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4551,10 +4551,10 @@
         <v>5.1106</v>
       </c>
       <c r="F133" t="n">
-        <v>0.0199</v>
+        <v>0.0189</v>
       </c>
       <c r="G133" t="n">
-        <v>99.61</v>
+        <v>99.63</v>
       </c>
     </row>
     <row r="134">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Obj indexing &gt; Sbj indexing</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4582,10 +4582,10 @@
         <v>3.5141</v>
       </c>
       <c r="F134" t="n">
-        <v>0.114</v>
+        <v>0.0512</v>
       </c>
       <c r="G134" t="n">
-        <v>96.76000000000001</v>
+        <v>98.54000000000001</v>
       </c>
     </row>
     <row r="135">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Adp-N &amp; N-Adj &gt; N-Gen</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4613,10 +4613,10 @@
         <v>3.8501</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0221</v>
+        <v>0.0263</v>
       </c>
       <c r="G135" t="n">
-        <v>99.42</v>
+        <v>99.31999999999999</v>
       </c>
     </row>
     <row r="136">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>N-Adp &amp; Adj-N &gt; Gen-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4644,10 +4644,10 @@
         <v>4.5929</v>
       </c>
       <c r="F136" t="n">
-        <v>0.0152</v>
+        <v>0.0149</v>
       </c>
       <c r="G136" t="n">
-        <v>99.67</v>
+        <v>99.68000000000001</v>
       </c>
     </row>
     <row r="137">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>N-Dem &gt; N-Adj</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4675,10 +4675,10 @@
         <v>2.2049</v>
       </c>
       <c r="F137" t="n">
-        <v>0.0513</v>
+        <v>0.0974</v>
       </c>
       <c r="G137" t="n">
-        <v>97.67</v>
+        <v>95.58</v>
       </c>
     </row>
     <row r="138">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>N-Num &gt; N-Adj</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4706,10 +4706,10 @@
         <v>4.0898</v>
       </c>
       <c r="F138" t="n">
-        <v>0.0221</v>
+        <v>0.0171</v>
       </c>
       <c r="G138" t="n">
-        <v>99.45999999999999</v>
+        <v>99.58</v>
       </c>
     </row>
     <row r="139">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>verb agreement &gt; agreement S</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4737,10 +4737,10 @@
         <v>4.0586</v>
       </c>
       <c r="F139" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0315</v>
       </c>
       <c r="G139" t="n">
-        <v>98.23</v>
+        <v>99.22</v>
       </c>
     </row>
     <row r="140">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Adp-N &amp; N-Dem &gt; N-Rel</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4768,10 +4768,10 @@
         <v>4.2505</v>
       </c>
       <c r="F140" t="n">
-        <v>0.2216</v>
+        <v>0.0793</v>
       </c>
       <c r="G140" t="n">
-        <v>94.79000000000001</v>
+        <v>98.14</v>
       </c>
     </row>
     <row r="141">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>N-Dem &gt; N-Rel</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4799,10 +4799,10 @@
         <v>2.9352</v>
       </c>
       <c r="F141" t="n">
-        <v>0.0185</v>
+        <v>0.0428</v>
       </c>
       <c r="G141" t="n">
-        <v>99.37</v>
+        <v>98.54000000000001</v>
       </c>
     </row>
     <row r="142">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>gender 2SG &gt; gender 3SG</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4830,10 +4830,10 @@
         <v>4.0674</v>
       </c>
       <c r="F142" t="n">
-        <v>0.8659</v>
+        <v>1.2527</v>
       </c>
       <c r="G142" t="n">
-        <v>78.70999999999999</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="143">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>N-Adp &amp; (Adj-N | Rel-N) &gt; Dem-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4861,7 +4861,7 @@
         <v>3.5859</v>
       </c>
       <c r="F143" t="n">
-        <v>0.0307</v>
+        <v>0.0309</v>
       </c>
       <c r="G143" t="n">
         <v>99.14</v>
@@ -4875,7 +4875,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>N-Adp &amp; (Adj-N | Rel-N) &gt; Num-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4892,10 +4892,10 @@
         <v>3.9912</v>
       </c>
       <c r="F144" t="n">
-        <v>0.0224</v>
+        <v>0.022</v>
       </c>
       <c r="G144" t="n">
-        <v>99.44</v>
+        <v>99.45</v>
       </c>
     </row>
     <row r="145">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>OV &gt; Adj-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4923,10 +4923,10 @@
         <v>5.3293</v>
       </c>
       <c r="F145" t="n">
-        <v>0.0388</v>
+        <v>0.0179</v>
       </c>
       <c r="G145" t="n">
-        <v>99.27</v>
+        <v>99.66</v>
       </c>
     </row>
     <row r="146">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>N-Rel &gt; N-Adj</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4954,10 +4954,10 @@
         <v>3.3336</v>
       </c>
       <c r="F146" t="n">
-        <v>0.0327</v>
+        <v>0.032</v>
       </c>
       <c r="G146" t="n">
-        <v>99.02</v>
+        <v>99.04000000000001</v>
       </c>
     </row>
     <row r="147">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SOV &amp; Det-N &gt; N-Adp</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4985,10 +4985,10 @@
         <v>2.3959</v>
       </c>
       <c r="F147" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0256</v>
       </c>
       <c r="G147" t="n">
-        <v>96.55</v>
+        <v>98.93000000000001</v>
       </c>
     </row>
     <row r="148">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>N-Num &gt; N-Rel</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5016,10 +5016,10 @@
         <v>4.6235</v>
       </c>
       <c r="F148" t="n">
-        <v>0.0213</v>
+        <v>0.033</v>
       </c>
       <c r="G148" t="n">
-        <v>99.54000000000001</v>
+        <v>99.29000000000001</v>
       </c>
     </row>
     <row r="149">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>no Adj Agr &gt; Gen-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5047,10 +5047,10 @@
         <v>2.4806</v>
       </c>
       <c r="F149" t="n">
-        <v>0.04</v>
+        <v>0.0437</v>
       </c>
       <c r="G149" t="n">
-        <v>98.39</v>
+        <v>98.23999999999999</v>
       </c>
     </row>
     <row r="150">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SVO/VSO &gt; V-like Pred Adj</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5078,10 +5078,10 @@
         <v>5.1389</v>
       </c>
       <c r="F150" t="n">
-        <v>0.0194</v>
+        <v>0.0193</v>
       </c>
       <c r="G150" t="n">
-        <v>99.62</v>
+        <v>99.63</v>
       </c>
     </row>
     <row r="151">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>gender Art &gt; number Art</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5109,10 +5109,10 @@
         <v>2.7192</v>
       </c>
       <c r="F151" t="n">
-        <v>3.8024</v>
+        <v>9.101000000000001</v>
       </c>
       <c r="G151" t="n">
-        <v>-39.83</v>
+        <v>-234.7</v>
       </c>
     </row>
     <row r="152">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>rigid order &amp; no case &gt; def Art</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5140,10 +5140,10 @@
         <v>2.9543</v>
       </c>
       <c r="F152" t="n">
-        <v>0.1039</v>
+        <v>0.0693</v>
       </c>
       <c r="G152" t="n">
-        <v>96.48</v>
+        <v>97.66</v>
       </c>
     </row>
     <row r="153">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>rigid order &gt; SV</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5171,10 +5171,10 @@
         <v>1.7623</v>
       </c>
       <c r="F153" t="n">
-        <v>0.0464</v>
+        <v>0.038</v>
       </c>
       <c r="G153" t="n">
-        <v>97.37</v>
+        <v>97.84</v>
       </c>
     </row>
     <row r="154">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>rigid order &gt; N-Adj</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5202,10 +5202,10 @@
         <v>1.9534</v>
       </c>
       <c r="F154" t="n">
-        <v>0.042</v>
+        <v>0.0577</v>
       </c>
       <c r="G154" t="n">
-        <v>97.84999999999999</v>
+        <v>97.05</v>
       </c>
     </row>
     <row r="155">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>nom/acc pronouns &gt; nom/acc nouns</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5233,10 +5233,10 @@
         <v>3.0338</v>
       </c>
       <c r="F155" t="n">
-        <v>0.0361</v>
+        <v>0.0341</v>
       </c>
       <c r="G155" t="n">
-        <v>98.81</v>
+        <v>98.88</v>
       </c>
     </row>
     <row r="156">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>s prefix &gt; o prefix &amp; no  o suffix (strong)</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5264,10 +5264,10 @@
         <v>4.5275</v>
       </c>
       <c r="F156" t="n">
-        <v>0.0238</v>
+        <v>0.0513</v>
       </c>
       <c r="G156" t="n">
-        <v>99.47</v>
+        <v>98.87</v>
       </c>
     </row>
     <row r="157">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>VS (trans. verb) &gt; VS (intrans. verb)</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5295,10 +5295,10 @@
         <v>3.5075</v>
       </c>
       <c r="F157" t="n">
-        <v>0.8694</v>
+        <v>0.8973</v>
       </c>
       <c r="G157" t="n">
-        <v>75.20999999999999</v>
+        <v>74.42</v>
       </c>
     </row>
     <row r="158">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>VS &amp; suffixal verb agree S &gt; suffixal verb agree P</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5326,10 +5326,10 @@
         <v>1.2733</v>
       </c>
       <c r="F158" t="n">
-        <v>0.5194</v>
+        <v>0.9765</v>
       </c>
       <c r="G158" t="n">
-        <v>59.21</v>
+        <v>23.31</v>
       </c>
     </row>
     <row r="159">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>inalienable possessive prefixes &gt; Gen-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5357,10 +5357,10 @@
         <v>3.5663</v>
       </c>
       <c r="F159" t="n">
-        <v>0.0457</v>
+        <v>0.0343</v>
       </c>
       <c r="G159" t="n">
-        <v>98.72</v>
+        <v>99.04000000000001</v>
       </c>
     </row>
     <row r="160">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SOV &gt; N-Adp</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5388,10 +5388,10 @@
         <v>4.2541</v>
       </c>
       <c r="F160" t="n">
-        <v>0.0215</v>
+        <v>0.0195</v>
       </c>
       <c r="G160" t="n">
-        <v>99.48999999999999</v>
+        <v>99.54000000000001</v>
       </c>
     </row>
     <row r="161">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Q-Sent &gt; Adp-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5419,10 +5419,10 @@
         <v>1.9978</v>
       </c>
       <c r="F161" t="n">
-        <v>0.0862</v>
+        <v>0.0621</v>
       </c>
       <c r="G161" t="n">
-        <v>95.69</v>
+        <v>96.89</v>
       </c>
     </row>
     <row r="162">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Trial &gt; Dual</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5450,10 +5450,10 @@
         <v>0.9302</v>
       </c>
       <c r="F162" t="n">
-        <v>2.4329</v>
+        <v>0.6424</v>
       </c>
       <c r="G162" t="n">
-        <v>-161.55</v>
+        <v>30.93</v>
       </c>
     </row>
     <row r="163">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Dual &gt; Plural</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5481,10 +5481,10 @@
         <v>4.0338</v>
       </c>
       <c r="F163" t="n">
-        <v>0.0567</v>
+        <v>0.0696</v>
       </c>
       <c r="G163" t="n">
-        <v>98.59</v>
+        <v>98.28</v>
       </c>
     </row>
     <row r="164">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>gender &gt; number</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5512,10 +5512,10 @@
         <v>3.1533</v>
       </c>
       <c r="F164" t="n">
-        <v>0.027</v>
+        <v>0.0244</v>
       </c>
       <c r="G164" t="n">
-        <v>99.14</v>
+        <v>99.23</v>
       </c>
     </row>
     <row r="165">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Gender Nouns &gt; Gender ProN</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5543,10 +5543,10 @@
         <v>2.4602</v>
       </c>
       <c r="F165" t="n">
-        <v>0.04</v>
+        <v>0.0376</v>
       </c>
       <c r="G165" t="n">
-        <v>98.38</v>
+        <v>98.47</v>
       </c>
     </row>
     <row r="166">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>gender (1) &gt; gender (2 &amp;| 3)</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5574,10 +5574,10 @@
         <v>1.1899</v>
       </c>
       <c r="F166" t="n">
-        <v>0.04</v>
+        <v>0.9502</v>
       </c>
       <c r="G166" t="n">
-        <v>96.64</v>
+        <v>20.14</v>
       </c>
     </row>
     <row r="167">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Adj agree noun &gt; Dem agree noun</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5605,10 +5605,10 @@
         <v>1.7738</v>
       </c>
       <c r="F167" t="n">
-        <v>0.0643</v>
+        <v>0.0611</v>
       </c>
       <c r="G167" t="n">
-        <v>96.37</v>
+        <v>96.56</v>
       </c>
     </row>
     <row r="168">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Du (noun) &gt; Du (pronoun)</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5636,10 +5636,10 @@
         <v>2.4277</v>
       </c>
       <c r="F168" t="n">
-        <v>0.0975</v>
+        <v>0.1867</v>
       </c>
       <c r="G168" t="n">
-        <v>95.98999999999999</v>
+        <v>92.31</v>
       </c>
     </row>
     <row r="169">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>obli (in)Def marking &gt; obli PL marking (noun)</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5667,10 +5667,10 @@
         <v>2.2296</v>
       </c>
       <c r="F169" t="n">
-        <v>0.0896</v>
+        <v>0.0592</v>
       </c>
       <c r="G169" t="n">
-        <v>95.98</v>
+        <v>97.34999999999999</v>
       </c>
     </row>
     <row r="170">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>tensed &gt; N-like Pred Adj</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5698,10 +5698,10 @@
         <v>2.7204</v>
       </c>
       <c r="F170" t="n">
-        <v>0.0347</v>
+        <v>0.0649</v>
       </c>
       <c r="G170" t="n">
-        <v>98.73</v>
+        <v>97.61</v>
       </c>
     </row>
     <row r="171">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>VSO &gt; person &amp; number inflection</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5729,10 +5729,10 @@
         <v>5.6176</v>
       </c>
       <c r="F171" t="n">
-        <v>1.8213</v>
+        <v>0.304</v>
       </c>
       <c r="G171" t="n">
-        <v>67.58</v>
+        <v>94.59</v>
       </c>
     </row>
     <row r="172">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>no case &gt; no morph tense | VO</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>OV -&gt; morph tense | case</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5791,10 +5791,10 @@
         <v>5.4887</v>
       </c>
       <c r="F173" t="n">
-        <v>0.0585</v>
+        <v>0.0226</v>
       </c>
       <c r="G173" t="n">
-        <v>98.93000000000001</v>
+        <v>99.59</v>
       </c>
     </row>
     <row r="174">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>case &gt; morph tense | OV</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5822,10 +5822,10 @@
         <v>3.5756</v>
       </c>
       <c r="F174" t="n">
-        <v>0.027</v>
+        <v>0.0278</v>
       </c>
       <c r="G174" t="n">
-        <v>99.23999999999999</v>
+        <v>99.22</v>
       </c>
     </row>
     <row r="175">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>no inflectional morph. &gt; fixed order of nominal args</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5853,10 +5853,10 @@
         <v>3.0269</v>
       </c>
       <c r="F175" t="n">
-        <v>0.0277</v>
+        <v>0.0285</v>
       </c>
       <c r="G175" t="n">
-        <v>99.08</v>
+        <v>99.06</v>
       </c>
     </row>
     <row r="176">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>no passive &gt; SOV</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5884,10 +5884,10 @@
         <v>3.6674</v>
       </c>
       <c r="F176" t="n">
-        <v>0.1488</v>
+        <v>0.0243</v>
       </c>
       <c r="G176" t="n">
-        <v>95.94</v>
+        <v>99.34</v>
       </c>
     </row>
     <row r="177">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ergative &gt; VSO | SOV</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5915,10 +5915,10 @@
         <v>4.4536</v>
       </c>
       <c r="F177" t="n">
-        <v>0.0842</v>
+        <v>0.0726</v>
       </c>
       <c r="G177" t="n">
-        <v>98.11</v>
+        <v>98.37</v>
       </c>
     </row>
     <row r="178">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SVO &gt; not ergative</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5946,10 +5946,10 @@
         <v>4.5319</v>
       </c>
       <c r="F178" t="n">
-        <v>0.0428</v>
+        <v>0.0459</v>
       </c>
       <c r="G178" t="n">
-        <v>99.06</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="179">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>verbal reciprocal/reflexive &gt; verb agreement with subject</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5977,10 +5977,10 @@
         <v>3.1597</v>
       </c>
       <c r="F179" t="n">
-        <v>0.0576</v>
+        <v>0.0416</v>
       </c>
       <c r="G179" t="n">
-        <v>98.18000000000001</v>
+        <v>98.68000000000001</v>
       </c>
     </row>
     <row r="180">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>weak plural &gt; numeral classifiers</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6008,10 +6008,10 @@
         <v>4.8004</v>
       </c>
       <c r="F180" t="n">
-        <v>0.0373</v>
+        <v>0.0137</v>
       </c>
       <c r="G180" t="n">
-        <v>99.22</v>
+        <v>99.70999999999999</v>
       </c>
     </row>
     <row r="181">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>many tenses &gt; no aspect</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6039,10 +6039,10 @@
         <v>2.3668</v>
       </c>
       <c r="F181" t="n">
-        <v>0.043</v>
+        <v>0.0538</v>
       </c>
       <c r="G181" t="n">
-        <v>98.18000000000001</v>
+        <v>97.73</v>
       </c>
     </row>
     <row r="182">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>N-Adj &gt; PRS overt copula “to be”</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6070,10 +6070,10 @@
         <v>4.0214</v>
       </c>
       <c r="F182" t="n">
-        <v>0.1143</v>
+        <v>0.0373</v>
       </c>
       <c r="G182" t="n">
-        <v>97.16</v>
+        <v>99.06999999999999</v>
       </c>
     </row>
     <row r="183">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>V-final &gt; no several articles</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6101,7 +6101,7 @@
         <v>5.2734</v>
       </c>
       <c r="F183" t="n">
-        <v>0.0137</v>
+        <v>0.0136</v>
       </c>
       <c r="G183" t="n">
         <v>99.73999999999999</v>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>V-initial &gt; several articles</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6132,10 +6132,10 @@
         <v>6.1999</v>
       </c>
       <c r="F184" t="n">
-        <v>0.91</v>
+        <v>0.6281</v>
       </c>
       <c r="G184" t="n">
-        <v>85.31999999999999</v>
+        <v>89.87</v>
       </c>
     </row>
     <row r="185">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>V-initial &gt; N-Gen</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6163,10 +6163,10 @@
         <v>5.6407</v>
       </c>
       <c r="F185" t="n">
-        <v>0.9435</v>
+        <v>0.4412</v>
       </c>
       <c r="G185" t="n">
-        <v>83.27</v>
+        <v>92.18000000000001</v>
       </c>
     </row>
     <row r="186">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>V-initial &gt; N-Rel</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6194,10 +6194,10 @@
         <v>5.7749</v>
       </c>
       <c r="F186" t="n">
-        <v>0.3148</v>
+        <v>0.1905</v>
       </c>
       <c r="G186" t="n">
-        <v>94.55</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="187">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SOV &amp; N-Art &gt; N-Art agr</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6225,10 +6225,10 @@
         <v>1.6023</v>
       </c>
       <c r="F187" t="n">
-        <v>0.7289</v>
+        <v>1.2223</v>
       </c>
       <c r="G187" t="n">
-        <v>54.51</v>
+        <v>23.71</v>
       </c>
     </row>
     <row r="188">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SOV &amp; N-Adj &gt; N-Adj agr</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6256,10 +6256,10 @@
         <v>4.1805</v>
       </c>
       <c r="F188" t="n">
-        <v>0.3223</v>
+        <v>0.2677</v>
       </c>
       <c r="G188" t="n">
-        <v>92.29000000000001</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="189">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>non-tensed &gt; no copula nom predicate</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6287,10 +6287,10 @@
         <v>3.4836</v>
       </c>
       <c r="F189" t="n">
-        <v>0.0235</v>
+        <v>0.0252</v>
       </c>
       <c r="G189" t="n">
-        <v>99.33</v>
+        <v>99.28</v>
       </c>
     </row>
     <row r="190">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>S-Comp &gt; SOV</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6318,10 +6318,10 @@
         <v>0.8995</v>
       </c>
       <c r="F190" t="n">
-        <v>0.0621</v>
+        <v>0.0638</v>
       </c>
       <c r="G190" t="n">
-        <v>93.09999999999999</v>
+        <v>92.91</v>
       </c>
     </row>
     <row r="191">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Rel-N | Adj-N &gt; Gen-N</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6349,10 +6349,10 @@
         <v>2.9949</v>
       </c>
       <c r="F191" t="n">
-        <v>0.0328</v>
+        <v>0.0303</v>
       </c>
       <c r="G191" t="n">
-        <v>98.90000000000001</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="192">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>non-affixed Gen-N &gt; OV</t>
+          <t>Supplementary Typological Trait Invariant</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6380,10 +6380,10 @@
         <v>3.6273</v>
       </c>
       <c r="F192" t="n">
-        <v>0.0297</v>
+        <v>0.031</v>
       </c>
       <c r="G192" t="n">
-        <v>99.18000000000001</v>
+        <v>99.14</v>
       </c>
     </row>
   </sheetData>

--- a/output/Supplementary_Table_S1_Global_Synthesis.xlsx
+++ b/output/Supplementary_Table_S1_Global_Synthesis.xlsx
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0001_OR_2AKA</t>
+          <t>0005KA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>SOV &amp; N-Gen &gt; N-Adj</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -487,24 +487,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4.3073</v>
+        <v>4.7977</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0172</v>
+        <v>0.0179</v>
       </c>
       <c r="G2" t="n">
-        <v>99.59999999999999</v>
+        <v>99.63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0001_OR_2BKA</t>
+          <t>0015BKA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>VO &gt; Mod-V</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -518,24 +518,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3.3722</v>
+        <v>5.3779</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0455</v>
+        <v>0.0191</v>
       </c>
       <c r="G3" t="n">
-        <v>98.65000000000001</v>
+        <v>99.64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0005KA</t>
+          <t>0055KA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>VSO &gt; Adp-N</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -549,24 +549,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4.7977</v>
+        <v>4.6431</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0179</v>
+        <v>0.146</v>
       </c>
       <c r="G4" t="n">
-        <v>99.63</v>
+        <v>96.86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0015AKA</t>
+          <t>0062AKA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Rel-N &gt; Adj-N</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -580,24 +580,24 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5.358</v>
+        <v>3.2377</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0257</v>
+        <v>0.0325</v>
       </c>
       <c r="G5" t="n">
-        <v>99.52</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0055KA</t>
+          <t>0067_OR_68KA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>VSO &amp; N-Adj &gt; N-Gen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -611,24 +611,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4.6431</v>
+        <v>4.3286</v>
       </c>
       <c r="F6" t="n">
-        <v>0.146</v>
+        <v>0.8068</v>
       </c>
       <c r="G6" t="n">
-        <v>96.86</v>
+        <v>81.36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0056KA</t>
+          <t>0070KA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Adp-N &amp; no SVO &amp; N-Adj &gt; N-Gen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -642,24 +642,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3.592</v>
+        <v>2.7683</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6432</v>
+        <v>2.1785</v>
       </c>
       <c r="G7" t="n">
-        <v>26.41</v>
+        <v>21.31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0057AKA</t>
+          <t>0107BKA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>OV &gt; Adj-N</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -673,24 +673,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3.7188</v>
+        <v>5.3293</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0829</v>
+        <v>0.0179</v>
       </c>
       <c r="G8" t="n">
-        <v>97.77</v>
+        <v>99.66</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0062AKA</t>
+          <t>0108KA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>OV &gt; Sent-Q</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -704,24 +704,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3.2377</v>
+        <v>5.2151</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0325</v>
+        <v>0.023</v>
       </c>
       <c r="G9" t="n">
-        <v>99</v>
+        <v>99.56</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0067_OR_68KA</t>
+          <t>0126NKA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>N-Num &gt; N-Rel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -735,24 +735,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4.3286</v>
+        <v>4.6235</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8068</v>
+        <v>0.033</v>
       </c>
       <c r="G10" t="n">
-        <v>81.36</v>
+        <v>99.29000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0070KA</t>
+          <t>0144KA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>no Adj Agr &gt; Gen-N</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -766,24 +766,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2.7683</v>
+        <v>2.4806</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1785</v>
+        <v>0.0437</v>
       </c>
       <c r="G11" t="n">
-        <v>21.31</v>
+        <v>98.23999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0072KA</t>
+          <t>0145KA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>SVO/VSO &gt; V-like Pred Adj</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -797,24 +797,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4.1821</v>
+        <v>5.1389</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0354</v>
+        <v>0.0193</v>
       </c>
       <c r="G12" t="n">
-        <v>99.15000000000001</v>
+        <v>99.63</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0074KA</t>
+          <t>0147KA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>V-like Attr Adj &gt; SVO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -828,24 +828,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4.4397</v>
+        <v>1.609</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8878</v>
+        <v>0.0579</v>
       </c>
       <c r="G13" t="n">
-        <v>57.48</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0091KA</t>
+          <t>0230CKA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>rigid order &gt; Adp-N</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -859,24 +859,24 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3.9625</v>
+        <v>2.0821</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0242</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>99.39</v>
+        <v>96.54000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0107AKA</t>
+          <t>0230FKA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>free order &gt; no Adp-N</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -890,24 +890,24 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5.2508</v>
+        <v>2.081</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0199</v>
+        <v>0.068</v>
       </c>
       <c r="G15" t="n">
-        <v>99.62</v>
+        <v>96.73</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0107CKA</t>
+          <t>0231AKA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>rigid order | no case &gt; gradation adj  function word</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -921,24 +921,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4.8632</v>
+        <v>2.7331</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0186</v>
+        <v>0.0528</v>
       </c>
       <c r="G16" t="n">
-        <v>99.62</v>
+        <v>98.06999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0108KA</t>
+          <t>0232KA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>rigid order &amp; no case &gt; def Art</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -952,24 +952,24 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5.2151</v>
+        <v>2.9543</v>
       </c>
       <c r="F17" t="n">
-        <v>0.023</v>
+        <v>0.0693</v>
       </c>
       <c r="G17" t="n">
-        <v>99.56</v>
+        <v>97.66</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0116KA</t>
+          <t>0238BKA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>rigid order &gt; N-Adj</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -983,24 +983,24 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.3053</v>
+        <v>1.9534</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0473</v>
+        <v>0.0577</v>
       </c>
       <c r="G18" t="n">
-        <v>97.95</v>
+        <v>97.05</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0121KA</t>
+          <t>0238DKA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>rigid order &gt; N-Rel</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1014,24 +1014,24 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4.3015</v>
+        <v>1.7659</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3778</v>
+        <v>0.1051</v>
       </c>
       <c r="G19" t="n">
-        <v>91.22</v>
+        <v>94.05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0147KA</t>
+          <t>0239AKA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>free order &gt;  case noun|pronoun</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1045,24 +1045,24 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.609</v>
+        <v>2.0996</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0579</v>
+        <v>0.0796</v>
       </c>
       <c r="G20" t="n">
-        <v>96.40000000000001</v>
+        <v>96.20999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0166KA</t>
+          <t>0239BKA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>free order &gt; number noun adj art</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1076,24 +1076,24 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3.6427</v>
+        <v>1.834</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0314</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>99.14</v>
+        <v>96.42</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0176KA</t>
+          <t>0239CKA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>free order &gt; gender (pro)noun adj art</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1107,24 +1107,24 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4.8968</v>
+        <v>2.0907</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0709</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>57.71</v>
+        <v>96.34999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0177KA</t>
+          <t>0240AKA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>ergative case &gt; Gen-N &amp; N-Adj</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1138,24 +1138,24 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3.0797</v>
+        <v>4.8242</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0362</v>
+        <v>0.1558</v>
       </c>
       <c r="G23" t="n">
-        <v>98.81999999999999</v>
+        <v>96.77</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0179AKA</t>
+          <t>0245BKA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>rigid order &amp; no inversion &gt; no inflection nouns</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1169,24 +1169,24 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.502</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0384</v>
+        <v>0.0548</v>
       </c>
       <c r="G24" t="n">
-        <v>98.90000000000001</v>
+        <v>94.04000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0179BKA</t>
+          <t>0247KA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>accusative &gt; gender</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1200,24 +1200,24 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3.8542</v>
+        <v>3.4121</v>
       </c>
       <c r="F25" t="n">
-        <v>1.4401</v>
+        <v>0.0317</v>
       </c>
       <c r="G25" t="n">
-        <v>62.64</v>
+        <v>99.06999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0230AKA</t>
+          <t>0260KA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>ergative &gt; prefixal personal conjugation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1231,24 +1231,24 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.0356</v>
+        <v>4.7484</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1214</v>
+        <v>0.1094</v>
       </c>
       <c r="G26" t="n">
-        <v>94.04000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0230BKA</t>
+          <t>0331AKA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>s prefix &gt; o prefix &amp; no  o suffix (strong)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1262,24 +1262,24 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.707</v>
+        <v>4.5275</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0601</v>
+        <v>0.0513</v>
       </c>
       <c r="G27" t="n">
-        <v>97.78</v>
+        <v>98.87</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0230EKA</t>
+          <t>0356KA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>verb agree S&amp;P suffixal &gt; SV</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1293,24 +1293,24 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3.1869</v>
+        <v>4.3424</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0266</v>
+        <v>1.9695</v>
       </c>
       <c r="G28" t="n">
-        <v>99.17</v>
+        <v>54.65</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0230FKA</t>
+          <t>0357KA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>VS &amp; suffixal verb agree S &gt; suffixal verb agree P</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1324,24 +1324,24 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2.081</v>
+        <v>1.2733</v>
       </c>
       <c r="F29" t="n">
-        <v>0.068</v>
+        <v>0.9765</v>
       </c>
       <c r="G29" t="n">
-        <v>96.73</v>
+        <v>23.31</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0231BKA</t>
+          <t>0365KA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>verb agree S &amp; prefixal verb agree P &gt; SV</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1355,24 +1355,24 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2.8291</v>
+        <v>4.4737</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0569</v>
+        <v>0.0578</v>
       </c>
       <c r="G30" t="n">
-        <v>97.98999999999999</v>
+        <v>98.70999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0239CKA</t>
+          <t>0439KA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>non-accusative alignment &gt; V-initial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1386,24 +1386,24 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2.0907</v>
+        <v>3.8434</v>
       </c>
       <c r="F31" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.4005</v>
       </c>
       <c r="G31" t="n">
-        <v>96.34999999999999</v>
+        <v>89.58</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0240AKA</t>
+          <t>0454KA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>inalienable possessive prefixes &gt; Gen-N</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1417,24 +1417,24 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4.8242</v>
+        <v>3.5663</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1558</v>
+        <v>0.0343</v>
       </c>
       <c r="G32" t="n">
-        <v>96.77</v>
+        <v>99.04000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0247KA</t>
+          <t>0504AKA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>prefixes &gt; Adp-N</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1448,24 +1448,24 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3.4121</v>
+        <v>1.8091</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0317</v>
+        <v>3.7493</v>
       </c>
       <c r="G33" t="n">
-        <v>99.06999999999999</v>
+        <v>-107.25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0332KA</t>
+          <t>0504BKA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>suffixes &gt; N-Adp</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1479,24 +1479,24 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3.5825</v>
+        <v>4.01</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0248</v>
+        <v>0.0413</v>
       </c>
       <c r="G34" t="n">
-        <v>99.31</v>
+        <v>98.97</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0356KA</t>
+          <t>0506KA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>inflection &gt; word formation</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1510,24 +1510,24 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4.3424</v>
+        <v>1.864</v>
       </c>
       <c r="F35" t="n">
-        <v>1.9695</v>
+        <v>3.888</v>
       </c>
       <c r="G35" t="n">
-        <v>54.65</v>
+        <v>-108.59</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0365KA</t>
+          <t>0511AKA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Trial &gt; Dual</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1541,24 +1541,24 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4.4737</v>
+        <v>0.9302</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0578</v>
+        <v>0.6424</v>
       </c>
       <c r="G36" t="n">
-        <v>98.70999999999999</v>
+        <v>30.93</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0386KA</t>
+          <t>0569KA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>no case (noun) &gt; article</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1572,24 +1572,24 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2.3485</v>
+        <v>3.2784</v>
       </c>
       <c r="F37" t="n">
-        <v>0.041</v>
+        <v>0.0312</v>
       </c>
       <c r="G37" t="n">
-        <v>98.25</v>
+        <v>99.05</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0446KA</t>
+          <t>0572KA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>obli (in)Def marking &gt; obli PL marking (noun)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1603,24 +1603,24 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2.566</v>
+        <v>2.2296</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0344</v>
+        <v>0.0592</v>
       </c>
       <c r="G38" t="n">
-        <v>98.66</v>
+        <v>97.34999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0493BKA</t>
+          <t>0573KA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>obli (in)Def marking &gt; no obli numeral classifier</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1634,24 +1634,24 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1.9639</v>
+        <v>2.5601</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0469</v>
+        <v>0.0598</v>
       </c>
       <c r="G39" t="n">
-        <v>97.61</v>
+        <v>97.66</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0506KA</t>
+          <t>0668KA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>SOV &gt; Sent-Q</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1665,24 +1665,24 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1.864</v>
+        <v>5.4762</v>
       </c>
       <c r="F40" t="n">
-        <v>3.888</v>
+        <v>0.0163</v>
       </c>
       <c r="G40" t="n">
-        <v>-108.59</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0507KA</t>
+          <t>0798KA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>tensed &gt; N-like Pred Adj</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1696,24 +1696,24 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3.6421</v>
+        <v>2.7204</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0328</v>
+        <v>0.0649</v>
       </c>
       <c r="G41" t="n">
-        <v>99.09999999999999</v>
+        <v>97.61</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0569KA</t>
+          <t>0837KA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>VSO &gt; person &amp; number inflection</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1727,24 +1727,24 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3.2784</v>
+        <v>5.6176</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0312</v>
+        <v>0.304</v>
       </c>
       <c r="G42" t="n">
-        <v>99.05</v>
+        <v>94.59</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0577KA</t>
+          <t>0889AKA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>OV &gt; suffixes</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1758,24 +1758,24 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2.1474</v>
+        <v>5.6372</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0418</v>
+        <v>0.0203</v>
       </c>
       <c r="G43" t="n">
-        <v>98.05</v>
+        <v>99.64</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0582KA</t>
+          <t>0889BKA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>VO &gt; prefixes</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1789,24 +1789,24 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2.6821</v>
+        <v>5.3508</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0517</v>
+        <v>0.0169</v>
       </c>
       <c r="G44" t="n">
-        <v>98.06999999999999</v>
+        <v>99.68000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0668KA</t>
+          <t>0917AKA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>VO &gt; Qpart-S</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1820,24 +1820,24 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5.4762</v>
+        <v>5.6748</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0163</v>
+        <v>0.0192</v>
       </c>
       <c r="G45" t="n">
-        <v>99.7</v>
+        <v>99.66</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0822KA</t>
+          <t>0917CKA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>OV &gt; Rel-N</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1851,24 +1851,24 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1.3651</v>
+        <v>5.1719</v>
       </c>
       <c r="F46" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>94.95</v>
+        <v>98.20999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0889BKA</t>
+          <t>0964AKA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>VO &gt; Art-N</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1882,24 +1882,24 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5.3508</v>
+        <v>5.5171</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0169</v>
+        <v>0.0184</v>
       </c>
       <c r="G47" t="n">
-        <v>99.68000000000001</v>
+        <v>99.67</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0917AKA</t>
+          <t>0964BKA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>OV &gt; N-Art</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1913,24 +1913,24 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5.6748</v>
+        <v>5.3598</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0192</v>
+        <v>0.023</v>
       </c>
       <c r="G48" t="n">
-        <v>99.66</v>
+        <v>99.56999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0917BKA</t>
+          <t>0983KA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>exceed comparative &gt; SVO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1944,24 +1944,24 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5.2069</v>
+        <v>1.5931</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0267</v>
+        <v>0.0443</v>
       </c>
       <c r="G49" t="n">
-        <v>99.48999999999999</v>
+        <v>97.22</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0964AKA</t>
+          <t>1028AKA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>OV -&gt; morph tense | case</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1975,24 +1975,24 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5.5171</v>
+        <v>5.4887</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0184</v>
+        <v>0.0226</v>
       </c>
       <c r="G50" t="n">
-        <v>99.67</v>
+        <v>99.59</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0982KA</t>
+          <t>1028BKA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>morph tense &gt; case | OV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2006,24 +2006,24 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2.4174</v>
+        <v>3.363</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0558</v>
+        <v>0.0294</v>
       </c>
       <c r="G51" t="n">
-        <v>97.69</v>
+        <v>99.13</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0983KA</t>
+          <t>1028CKA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>case &gt; morph tense | OV</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2037,24 +2037,24 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1.5931</v>
+        <v>3.5756</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0443</v>
+        <v>0.0278</v>
       </c>
       <c r="G52" t="n">
-        <v>97.22</v>
+        <v>99.22</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1027AKA</t>
+          <t>1111KA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>no inflectional morph. &gt; fixed order of nominal args</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2068,24 +2068,24 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4.9982</v>
+        <v>3.0269</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0195</v>
+        <v>0.0285</v>
       </c>
       <c r="G53" t="n">
-        <v>99.61</v>
+        <v>99.06</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1027BKA</t>
+          <t>1142AKA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>passive &gt; SVO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2099,24 +2099,24 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3.1951</v>
+        <v>3.6563</v>
       </c>
       <c r="F54" t="n">
-        <v>0.033</v>
+        <v>0.0259</v>
       </c>
       <c r="G54" t="n">
-        <v>98.97</v>
+        <v>99.29000000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1028BKA</t>
+          <t>1142BKA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>no passive &gt; SOV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2130,24 +2130,24 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3.363</v>
+        <v>3.6674</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0294</v>
+        <v>0.0243</v>
       </c>
       <c r="G55" t="n">
-        <v>99.13</v>
+        <v>99.34</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1114KA</t>
+          <t>1216KA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>N-Adp &gt; case (noun)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2161,24 +2161,24 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4.5168</v>
+        <v>3.9312</v>
       </c>
       <c r="F56" t="n">
-        <v>0.016</v>
+        <v>0.0238</v>
       </c>
       <c r="G56" t="n">
-        <v>99.65000000000001</v>
+        <v>99.39</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1142AKA</t>
+          <t>1334AKA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Adp-N &amp; Rel-N &gt; Gen-N</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2192,24 +2192,24 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3.6563</v>
+        <v>1.786</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0259</v>
+        <v>0.0941</v>
       </c>
       <c r="G57" t="n">
-        <v>99.29000000000001</v>
+        <v>94.73</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1163KA</t>
+          <t>1334BKA</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Adp-N &amp; Rel-N &amp; Gen-N &gt; Adj-N</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1.2682</v>
+        <v>4.8257</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0613</v>
+        <v>0.263</v>
       </c>
       <c r="G58" t="n">
-        <v>95.17</v>
+        <v>94.55</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1216KA</t>
+          <t>1334CKA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Adp-N &amp; Rel-N &amp; Gen-N &amp; Adj-N &gt; Dem-N</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2254,24 +2254,24 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3.9312</v>
+        <v>3.3497</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0238</v>
+        <v>0.5026</v>
       </c>
       <c r="G59" t="n">
-        <v>99.39</v>
+        <v>85</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1334AKA</t>
+          <t>1349KA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>weak plural &gt; numeral classifiers</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1.786</v>
+        <v>4.8004</v>
       </c>
       <c r="F60" t="n">
-        <v>0.0941</v>
+        <v>0.0137</v>
       </c>
       <c r="G60" t="n">
-        <v>94.73</v>
+        <v>99.70999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>verb HAVE &gt; SVO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2328,12 +2328,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1415KA</t>
+          <t>1430KA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>N-poss suf &gt; no PRS overt copula “to be”</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2347,24 +2347,24 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3.471</v>
+        <v>3.3706</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0403</v>
+        <v>0.029</v>
       </c>
       <c r="G62" t="n">
-        <v>98.84</v>
+        <v>99.14</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1427KA</t>
+          <t>1434KA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>many tenses &gt; no aspect</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2378,24 +2378,24 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4.0676</v>
+        <v>2.3668</v>
       </c>
       <c r="F63" t="n">
-        <v>1.5818</v>
+        <v>0.0538</v>
       </c>
       <c r="G63" t="n">
-        <v>61.11</v>
+        <v>97.73</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1430KA</t>
+          <t>1436KA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>N-Adj &gt; PRS overt copula “to be”</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2409,24 +2409,24 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3.3706</v>
+        <v>4.0214</v>
       </c>
       <c r="F64" t="n">
-        <v>0.029</v>
+        <v>0.0373</v>
       </c>
       <c r="G64" t="n">
-        <v>99.14</v>
+        <v>99.06999999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1431NKA</t>
+          <t>1499KA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>SVC &gt; little inflection</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2440,24 +2440,24 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3.067</v>
+        <v>2.2427</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0297</v>
+        <v>0.0521</v>
       </c>
       <c r="G65" t="n">
-        <v>99.03</v>
+        <v>97.68000000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1499KA</t>
+          <t>1531KA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>V-initial &gt; prefixes</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2471,24 +2471,24 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2.2427</v>
+        <v>5.8722</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0521</v>
+        <v>0.1454</v>
       </c>
       <c r="G66" t="n">
-        <v>97.68000000000001</v>
+        <v>97.52</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1531KA</t>
+          <t>1534KA</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>V-initial &gt; Q-Sent</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2502,13 +2502,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5.8722</v>
+        <v>6.1396</v>
       </c>
       <c r="F67" t="n">
-        <v>0.1454</v>
+        <v>0.3314</v>
       </c>
       <c r="G67" t="n">
-        <v>97.52</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>V-initial &gt; C-Sent</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2545,12 +2545,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1544KA</t>
+          <t>1546AKA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>V-final &gt; more Adj-N agreement</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2564,24 +2564,24 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5.8409</v>
+        <v>5.3949</v>
       </c>
       <c r="F69" t="n">
-        <v>0.1836</v>
+        <v>0.0185</v>
       </c>
       <c r="G69" t="n">
-        <v>96.86</v>
+        <v>99.66</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1545KA</t>
+          <t>1546BKA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>V-initial &gt; less Adj-N agreement</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2595,24 +2595,24 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5.7574</v>
+        <v>6.6938</v>
       </c>
       <c r="F70" t="n">
-        <v>0.23</v>
+        <v>0.4802</v>
       </c>
       <c r="G70" t="n">
-        <v>96</v>
+        <v>92.83</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1559KA</t>
+          <t>1548AKA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>V-final &gt; no several articles</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2626,24 +2626,24 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5.6687</v>
+        <v>5.2734</v>
       </c>
       <c r="F71" t="n">
-        <v>0.2846</v>
+        <v>0.0136</v>
       </c>
       <c r="G71" t="n">
-        <v>94.98</v>
+        <v>99.73999999999999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1589KA</t>
+          <t>1548BKA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>V-initial &gt; several articles</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2657,24 +2657,24 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4.9031</v>
+        <v>6.1999</v>
       </c>
       <c r="F72" t="n">
-        <v>0.0158</v>
+        <v>0.6281</v>
       </c>
       <c r="G72" t="n">
-        <v>99.68000000000001</v>
+        <v>89.87</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1593KA</t>
+          <t>1549KA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>V-initial &gt; N-Gen</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2688,24 +2688,24 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1.9558</v>
+        <v>5.6407</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0664</v>
+        <v>0.4412</v>
       </c>
       <c r="G73" t="n">
-        <v>96.59999999999999</v>
+        <v>92.18000000000001</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1610KA</t>
+          <t>1559KA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>V-initial &gt; passive voice</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2719,24 +2719,24 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4.2533</v>
+        <v>5.6687</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0445</v>
+        <v>0.2846</v>
       </c>
       <c r="G74" t="n">
-        <v>98.95</v>
+        <v>94.98</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1611KA</t>
+          <t>1560KA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>V-initial &gt; no verb agreement | agreement 2 NPs</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2750,24 +2750,24 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3.5488</v>
+        <v>5.9305</v>
       </c>
       <c r="F75" t="n">
-        <v>0.025</v>
+        <v>2.0066</v>
       </c>
       <c r="G75" t="n">
-        <v>99.3</v>
+        <v>66.16</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1621KA</t>
+          <t>1561KA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>V-initial &gt; no overt copula</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2781,24 +2781,24 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1.2332</v>
+        <v>6.0198</v>
       </c>
       <c r="F76" t="n">
-        <v>0.1768</v>
+        <v>1.1105</v>
       </c>
       <c r="G76" t="n">
-        <v>85.66</v>
+        <v>81.55</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1741KA</t>
+          <t>1589KA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>V-final &gt; postposing &amp; suffixes</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2812,24 +2812,24 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3.1169</v>
+        <v>4.9031</v>
       </c>
       <c r="F77" t="n">
-        <v>0.036</v>
+        <v>0.0158</v>
       </c>
       <c r="G77" t="n">
-        <v>98.84</v>
+        <v>99.68000000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1994CKA</t>
+          <t>1593KA</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>internal relative clause &gt; null anaphora</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2843,24 +2843,24 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3.722</v>
+        <v>1.9558</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0311</v>
+        <v>0.0664</v>
       </c>
       <c r="G78" t="n">
-        <v>99.16</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2012KA</t>
+          <t>1610KA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>verb-patient agreement &gt; V-initial | V-final</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2874,1672 +2874,1672 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2.6491</v>
+        <v>4.2533</v>
       </c>
       <c r="F79" t="n">
-        <v>0.0992</v>
+        <v>0.0445</v>
       </c>
       <c r="G79" t="n">
-        <v>96.25</v>
+        <v>98.95</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0015BKA</t>
+          <t>1612AKA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>SOV &amp; N-Art &gt; N-Art agr</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Consensus Non-Significant</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Non-Significant</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5.3779</v>
+        <v>1.6023</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0191</v>
+        <v>1.2223</v>
       </c>
       <c r="G80" t="n">
-        <v>99.64</v>
+        <v>23.71</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0057BKA</t>
+          <t>1612BKA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>SOV &amp; N-Adj &gt; N-Adj agr</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Consensus Non-Significant</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Non-Significant</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3.8289</v>
+        <v>4.1805</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0245</v>
+        <v>0.2677</v>
       </c>
       <c r="G81" t="n">
-        <v>99.36</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0062BKA</t>
+          <t>1621KA</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Adj &gt; no sortal classifiers</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Consensus Non-Significant</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Non-Significant</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3.1413</v>
+        <v>1.2332</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0368</v>
+        <v>0.1768</v>
       </c>
       <c r="G82" t="n">
-        <v>98.83</v>
+        <v>85.66</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0065_OR_66KA</t>
+          <t>1653KA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>non-tensed &gt; no copula nom predicate</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Consensus Non-Significant</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Non-Significant</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4.865</v>
+        <v>3.4836</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0202</v>
+        <v>0.0252</v>
       </c>
       <c r="G83" t="n">
-        <v>99.59</v>
+        <v>99.28</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0096KA</t>
+          <t>1667BKA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Comp-S &gt; VSO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Consensus Non-Significant</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Non-Significant</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3.2227</v>
+        <v>2.4502</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0309</v>
+        <v>0.0333</v>
       </c>
       <c r="G84" t="n">
-        <v>99.04000000000001</v>
+        <v>98.64</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0101KA</t>
+          <t>1827KA</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Rel-N | Adj-N &gt; Gen-N</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Consensus Non-Significant</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Non-Significant</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4.7382</v>
+        <v>2.9949</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0342</v>
+        <v>0.0303</v>
       </c>
       <c r="G85" t="n">
-        <v>99.28</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0173KA</t>
+          <t>1994CKA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>non-affixed Gen-N &gt; verbal prefixes pers um</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Consensus Non-Significant</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Non-Significant</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3.417</v>
+        <v>3.722</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0302</v>
+        <v>0.0311</v>
       </c>
       <c r="G86" t="n">
-        <v>99.12</v>
+        <v>99.16</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0174KA</t>
+          <t>2012KA</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>switch-reference marking &gt; accusitive</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Consensus Non-Significant</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Non-Significant</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4.0499</v>
+        <v>2.6491</v>
       </c>
       <c r="F87" t="n">
-        <v>0.3563</v>
+        <v>0.0992</v>
       </c>
       <c r="G87" t="n">
-        <v>91.2</v>
+        <v>96.25</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0175KA</t>
+          <t>0001_OR_2AKA</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Adp-N &gt; N-Gen</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5.1177</v>
+        <v>4.3073</v>
       </c>
       <c r="F88" t="n">
-        <v>0.5793</v>
+        <v>0.0172</v>
       </c>
       <c r="G88" t="n">
-        <v>88.68000000000001</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0178KA</t>
+          <t>0015AKA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>OV &gt; V-Mod</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3.7005</v>
+        <v>5.358</v>
       </c>
       <c r="F89" t="n">
-        <v>0.0253</v>
+        <v>0.0257</v>
       </c>
       <c r="G89" t="n">
-        <v>99.31999999999999</v>
+        <v>99.52</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0183KA</t>
+          <t>0045KA</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Obj indexing &gt; Sbj indexing</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2.9806</v>
+        <v>3.5141</v>
       </c>
       <c r="F90" t="n">
-        <v>0.0457</v>
+        <v>0.0512</v>
       </c>
       <c r="G90" t="n">
-        <v>98.47</v>
+        <v>98.54000000000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0228KA</t>
+          <t>0057AKA</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Adj-N &gt; Num-N</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3.1125</v>
+        <v>3.7188</v>
       </c>
       <c r="F91" t="n">
-        <v>0.0275</v>
+        <v>0.0829</v>
       </c>
       <c r="G91" t="n">
-        <v>99.12</v>
+        <v>97.77</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0229KA</t>
+          <t>0057BKA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Adj-N &gt; Dem-N</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2.2466</v>
+        <v>3.8289</v>
       </c>
       <c r="F92" t="n">
-        <v>0.0412</v>
+        <v>0.0245</v>
       </c>
       <c r="G92" t="n">
-        <v>98.17</v>
+        <v>99.36</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0230CKA</t>
+          <t>0062BKA</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Rel-N &gt; N-Adp</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2.0821</v>
+        <v>3.1413</v>
       </c>
       <c r="F93" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0368</v>
       </c>
       <c r="G93" t="n">
-        <v>96.54000000000001</v>
+        <v>98.83</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0230DKA</t>
+          <t>0065_OR_66KA</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>SOV &amp; Adj-N &gt; Gen-N</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2.0464</v>
+        <v>4.865</v>
       </c>
       <c r="F94" t="n">
-        <v>0.1251</v>
+        <v>0.0202</v>
       </c>
       <c r="G94" t="n">
-        <v>93.89</v>
+        <v>99.59</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0231AKA</t>
+          <t>0069KA</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Adp-N &amp; N-Adj &gt; N-Gen</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2.7331</v>
+        <v>3.8501</v>
       </c>
       <c r="F95" t="n">
-        <v>0.0528</v>
+        <v>0.0263</v>
       </c>
       <c r="G95" t="n">
-        <v>98.06999999999999</v>
+        <v>99.31999999999999</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0237AKA</t>
+          <t>0071KA</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>N-Adp &amp; Adj-N &gt; Gen-N</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2.1665</v>
+        <v>4.5929</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0356</v>
+        <v>0.0149</v>
       </c>
       <c r="G96" t="n">
-        <v>98.36</v>
+        <v>99.68000000000001</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0238DKA</t>
+          <t>0072KA</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Adp-N &amp; N-Dem &gt; N-Adj</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1.7659</v>
+        <v>4.1821</v>
       </c>
       <c r="F97" t="n">
-        <v>0.1051</v>
+        <v>0.0354</v>
       </c>
       <c r="G97" t="n">
-        <v>94.05</v>
+        <v>99.15000000000001</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0239AKA</t>
+          <t>0073KA</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>N-Dem &gt; N-Adj</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2.0996</v>
+        <v>2.2049</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0796</v>
+        <v>0.0974</v>
       </c>
       <c r="G98" t="n">
-        <v>96.20999999999999</v>
+        <v>95.58</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0239BKA</t>
+          <t>0074KA</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Adp-N &amp; N-Num &gt; N-Adj</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1.834</v>
+        <v>4.4397</v>
       </c>
       <c r="F99" t="n">
-        <v>0.06569999999999999</v>
+        <v>1.8878</v>
       </c>
       <c r="G99" t="n">
-        <v>96.42</v>
+        <v>57.48</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0245AKA</t>
+          <t>0075KA</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>N-Num &gt; N-Adj</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1.894</v>
+        <v>4.0898</v>
       </c>
       <c r="F100" t="n">
-        <v>0.06</v>
+        <v>0.0171</v>
       </c>
       <c r="G100" t="n">
-        <v>96.83</v>
+        <v>99.58</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0245BKA</t>
+          <t>0084KA</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>verb agreement &gt; agreement S</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9199000000000001</v>
+        <v>4.0586</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0548</v>
+        <v>0.0315</v>
       </c>
       <c r="G101" t="n">
-        <v>94.04000000000001</v>
+        <v>99.22</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0260KA</t>
+          <t>0087KA</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Adp-N &amp; N-Dem &gt; N-Rel</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4.7484</v>
+        <v>4.2505</v>
       </c>
       <c r="F102" t="n">
-        <v>0.1094</v>
+        <v>0.0793</v>
       </c>
       <c r="G102" t="n">
-        <v>97.7</v>
+        <v>98.14</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0276KA</t>
+          <t>0091KA</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Adp-N &amp; N-Adj &gt; N-Rel</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2.1666</v>
+        <v>3.9625</v>
       </c>
       <c r="F103" t="n">
-        <v>0.0362</v>
+        <v>0.0242</v>
       </c>
       <c r="G103" t="n">
-        <v>98.33</v>
+        <v>99.39</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0328KA</t>
+          <t>0093KA</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>gender 2SG &gt; gender 3SG</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4.0832</v>
+        <v>4.0674</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0155</v>
+        <v>1.2527</v>
       </c>
       <c r="G104" t="n">
-        <v>99.62</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0331BKA</t>
+          <t>0095AKA</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>N-Adp &amp; (Adj-N | Rel-N) &gt; Dem-N</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>3.9487</v>
+        <v>3.5859</v>
       </c>
       <c r="F105" t="n">
-        <v>0.032</v>
+        <v>0.0309</v>
       </c>
       <c r="G105" t="n">
-        <v>99.19</v>
+        <v>99.14</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0423KA</t>
+          <t>0096KA</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>N-Adp &amp; (Adj-N | Rel-N) &gt; PossPron-N</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5.5622</v>
+        <v>3.2227</v>
       </c>
       <c r="F106" t="n">
-        <v>0.0199</v>
+        <v>0.0309</v>
       </c>
       <c r="G106" t="n">
-        <v>99.64</v>
+        <v>99.04000000000001</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0439KA</t>
+          <t>0101KA</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>N-Gen &gt; N-Adj</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3.8434</v>
+        <v>4.7382</v>
       </c>
       <c r="F107" t="n">
-        <v>0.4005</v>
+        <v>0.0342</v>
       </c>
       <c r="G107" t="n">
-        <v>89.58</v>
+        <v>99.28</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0504AKA</t>
+          <t>0107AKA</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>VO &gt; N-Rel</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1.8091</v>
+        <v>5.2508</v>
       </c>
       <c r="F108" t="n">
-        <v>3.7493</v>
+        <v>0.0199</v>
       </c>
       <c r="G108" t="n">
-        <v>-107.25</v>
+        <v>99.62</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0504BKA</t>
+          <t>0107CKA</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>VO &gt; N-Gen</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4.01</v>
+        <v>4.8632</v>
       </c>
       <c r="F109" t="n">
-        <v>0.0413</v>
+        <v>0.0186</v>
       </c>
       <c r="G109" t="n">
-        <v>98.97</v>
+        <v>99.62</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0573KA</t>
+          <t>0110KA</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>N-Rel &gt; N-Adj</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2.5601</v>
+        <v>3.3336</v>
       </c>
       <c r="F110" t="n">
-        <v>0.0598</v>
+        <v>0.032</v>
       </c>
       <c r="G110" t="n">
-        <v>97.66</v>
+        <v>99.04000000000001</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0612KA</t>
+          <t>0125KA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>SOV &amp; Det-N &gt; N-Adp</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2.4176</v>
+        <v>2.3959</v>
       </c>
       <c r="F111" t="n">
-        <v>0.0252</v>
+        <v>0.0256</v>
       </c>
       <c r="G111" t="n">
-        <v>98.95999999999999</v>
+        <v>98.93000000000001</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0889AKA</t>
+          <t>0166KA</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>pref-V Obj &gt; V Agr Sbj</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5.6372</v>
+        <v>3.6427</v>
       </c>
       <c r="F112" t="n">
-        <v>0.0203</v>
+        <v>0.0314</v>
       </c>
       <c r="G112" t="n">
-        <v>99.64</v>
+        <v>99.14</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0917CKA</t>
+          <t>0173KA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Adp-N &amp; N-Dem &gt; N-Gen</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5.1719</v>
+        <v>3.417</v>
       </c>
       <c r="F113" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.0302</v>
       </c>
       <c r="G113" t="n">
-        <v>98.20999999999999</v>
+        <v>99.12</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0964BKA</t>
+          <t>0175KA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Adp-N &amp; N-Gen &gt; N-Rel</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5.3598</v>
+        <v>5.1177</v>
       </c>
       <c r="F114" t="n">
-        <v>0.023</v>
+        <v>0.5793</v>
       </c>
       <c r="G114" t="n">
-        <v>99.56999999999999</v>
+        <v>88.68000000000001</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1053KA</t>
+          <t>0176KA</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>N-Gen &gt; N-Rel</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1.745</v>
+        <v>4.8968</v>
       </c>
       <c r="F115" t="n">
-        <v>0.06710000000000001</v>
+        <v>2.0709</v>
       </c>
       <c r="G115" t="n">
-        <v>96.15000000000001</v>
+        <v>57.71</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1152KA</t>
+          <t>0177KA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>N-Adp &amp; Dem-N &gt; Gen-N</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2.5423</v>
+        <v>3.0797</v>
       </c>
       <c r="F116" t="n">
-        <v>0.0439</v>
+        <v>0.0362</v>
       </c>
       <c r="G116" t="n">
-        <v>98.27</v>
+        <v>98.81999999999999</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1334BKA</t>
+          <t>0178KA</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>N-Adp &amp; Num-N &gt; Gen-N</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4.8257</v>
+        <v>3.7005</v>
       </c>
       <c r="F117" t="n">
-        <v>0.263</v>
+        <v>0.0253</v>
       </c>
       <c r="G117" t="n">
-        <v>94.55</v>
+        <v>99.31999999999999</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1334CKA</t>
+          <t>0179AKA</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>gender Adj &gt; number Adj</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3.3497</v>
+        <v>3.502</v>
       </c>
       <c r="F118" t="n">
-        <v>0.5026</v>
+        <v>0.0384</v>
       </c>
       <c r="G118" t="n">
-        <v>85</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1431MKA</t>
+          <t>0179BKA</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>gender Dem &gt; number Dem</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2.9014</v>
+        <v>3.8542</v>
       </c>
       <c r="F119" t="n">
-        <v>0.0441</v>
+        <v>1.4401</v>
       </c>
       <c r="G119" t="n">
-        <v>98.48</v>
+        <v>62.64</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1534KA</t>
+          <t>0179CKA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>gender Art &gt; number Art</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6.1396</v>
+        <v>2.7192</v>
       </c>
       <c r="F120" t="n">
-        <v>0.3314</v>
+        <v>9.101000000000001</v>
       </c>
       <c r="G120" t="n">
-        <v>94.59999999999999</v>
+        <v>-234.7</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1546AKA</t>
+          <t>0183KA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>case Nouns &gt; case PronN</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5.3949</v>
+        <v>2.9806</v>
       </c>
       <c r="F121" t="n">
-        <v>0.0185</v>
+        <v>0.0457</v>
       </c>
       <c r="G121" t="n">
-        <v>99.66</v>
+        <v>98.47</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1546BKA</t>
+          <t>0228KA</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>nominal case &gt; verbal inflection</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6.6938</v>
+        <v>3.1125</v>
       </c>
       <c r="F122" t="n">
-        <v>0.4802</v>
+        <v>0.0275</v>
       </c>
       <c r="G122" t="n">
-        <v>92.83</v>
+        <v>99.12</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1560KA</t>
+          <t>0229KA</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>nominal number &gt; nominal case</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5.9305</v>
+        <v>2.2466</v>
       </c>
       <c r="F123" t="n">
-        <v>2.0066</v>
+        <v>0.0412</v>
       </c>
       <c r="G123" t="n">
-        <v>66.16</v>
+        <v>98.17</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1561KA</t>
+          <t>0230BKA</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>no case &gt; Adp-N</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6.0198</v>
+        <v>2.707</v>
       </c>
       <c r="F124" t="n">
-        <v>1.1105</v>
+        <v>0.0601</v>
       </c>
       <c r="G124" t="n">
-        <v>81.55</v>
+        <v>97.78</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1586KA</t>
+          <t>0230EKA</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>case &gt; no Adp-N</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>3.5375</v>
+        <v>3.1869</v>
       </c>
       <c r="F125" t="n">
-        <v>0.0325</v>
+        <v>0.0266</v>
       </c>
       <c r="G125" t="n">
-        <v>99.08</v>
+        <v>99.17</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1591KA</t>
+          <t>0231BKA</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>free order | case &gt; gradation adj inflect</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1.1324</v>
+        <v>2.8291</v>
       </c>
       <c r="F126" t="n">
-        <v>0.101</v>
+        <v>0.0569</v>
       </c>
       <c r="G126" t="n">
-        <v>91.08</v>
+        <v>97.98999999999999</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1592KA</t>
+          <t>0237AKA</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>number Adj &gt; number noun</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1.3654</v>
+        <v>2.1665</v>
       </c>
       <c r="F127" t="n">
-        <v>0.0452</v>
+        <v>0.0356</v>
       </c>
       <c r="G127" t="n">
-        <v>96.69</v>
+        <v>98.36</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1612CKA</t>
+          <t>0238AKA</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>rigid order &gt; SV</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4.4998</v>
+        <v>1.7623</v>
       </c>
       <c r="F128" t="n">
-        <v>0.8339</v>
+        <v>0.038</v>
       </c>
       <c r="G128" t="n">
-        <v>81.47</v>
+        <v>97.84</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1612DKA</t>
+          <t>0276KA</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>number (adjective | verb) &gt; number (noun)</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3.332</v>
+        <v>2.1666</v>
       </c>
       <c r="F129" t="n">
-        <v>0.1745</v>
+        <v>0.0362</v>
       </c>
       <c r="G129" t="n">
-        <v>94.76000000000001</v>
+        <v>98.33</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1667BKA</t>
+          <t>0320KA</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>nom/acc pronouns &gt; nom/acc nouns</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2.4502</v>
+        <v>3.0338</v>
       </c>
       <c r="F130" t="n">
-        <v>0.0333</v>
+        <v>0.0341</v>
       </c>
       <c r="G130" t="n">
-        <v>98.64</v>
+        <v>98.88</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1994AKA</t>
+          <t>0328KA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>verb agr S prefix &gt; verb agr P</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>3.6364</v>
+        <v>4.0832</v>
       </c>
       <c r="F131" t="n">
-        <v>0.0266</v>
+        <v>0.0155</v>
       </c>
       <c r="G131" t="n">
-        <v>99.27</v>
+        <v>99.62</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1994DKA</t>
+          <t>0331BKA</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>s prefix &gt; o prefix | o suffix (weak)</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Rescued Universals (3D Bounded)</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Significant (3D Only)</t>
+          <t>Significant (Both)</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3.5193</v>
+        <v>3.9487</v>
       </c>
       <c r="F132" t="n">
-        <v>0.0315</v>
+        <v>0.032</v>
       </c>
       <c r="G132" t="n">
-        <v>99.11</v>
+        <v>99.19</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0008KA</t>
+          <t>0332KA</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>o suffix &gt; s suffix</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4548,29 +4548,29 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5.1106</v>
+        <v>3.5825</v>
       </c>
       <c r="F133" t="n">
-        <v>0.0189</v>
+        <v>0.0248</v>
       </c>
       <c r="G133" t="n">
-        <v>99.63</v>
+        <v>99.31</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>0045KA</t>
+          <t>0344KA</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>VS (trans. verb) &gt; VS (intrans. verb)</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4579,29 +4579,29 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3.5141</v>
+        <v>3.5075</v>
       </c>
       <c r="F134" t="n">
-        <v>0.0512</v>
+        <v>0.8973</v>
       </c>
       <c r="G134" t="n">
-        <v>98.54000000000001</v>
+        <v>74.42</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>0069KA</t>
+          <t>0386KA</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>nominal inflection &gt; verbal inflection</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4610,29 +4610,29 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3.8501</v>
+        <v>2.3485</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0263</v>
+        <v>0.041</v>
       </c>
       <c r="G135" t="n">
-        <v>99.31999999999999</v>
+        <v>98.25</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>0071KA</t>
+          <t>0423KA</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Adp-N &amp; no SOV &gt; N-Rel</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4641,29 +4641,29 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4.5929</v>
+        <v>5.5622</v>
       </c>
       <c r="F136" t="n">
-        <v>0.0149</v>
+        <v>0.0199</v>
       </c>
       <c r="G136" t="n">
-        <v>99.68000000000001</v>
+        <v>99.64</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>0073KA</t>
+          <t>0446KA</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>V-final | free &gt; N-Adp | case</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4672,29 +4672,29 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2.2049</v>
+        <v>2.566</v>
       </c>
       <c r="F137" t="n">
-        <v>0.0974</v>
+        <v>0.0344</v>
       </c>
       <c r="G137" t="n">
-        <v>95.58</v>
+        <v>98.66</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>0075KA</t>
+          <t>0489KA</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>SOV &gt; N-Adp</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4703,29 +4703,29 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4.0898</v>
+        <v>4.2541</v>
       </c>
       <c r="F138" t="n">
-        <v>0.0171</v>
+        <v>0.0195</v>
       </c>
       <c r="G138" t="n">
-        <v>99.58</v>
+        <v>99.54000000000001</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>0084KA</t>
+          <t>0493AKA</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Q-Sent &gt; Adp-N</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4734,29 +4734,29 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4.0586</v>
+        <v>1.9978</v>
       </c>
       <c r="F139" t="n">
-        <v>0.0315</v>
+        <v>0.0621</v>
       </c>
       <c r="G139" t="n">
-        <v>99.22</v>
+        <v>96.89</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>0087KA</t>
+          <t>0493BKA</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Sent-Q &gt; N-Adp</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4765,29 +4765,29 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4.2505</v>
+        <v>1.9639</v>
       </c>
       <c r="F140" t="n">
-        <v>0.0793</v>
+        <v>0.0469</v>
       </c>
       <c r="G140" t="n">
-        <v>98.14</v>
+        <v>97.61</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>0088KA</t>
+          <t>0511BKA</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Dual &gt; Plural</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4796,29 +4796,29 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2.9352</v>
+        <v>4.0338</v>
       </c>
       <c r="F141" t="n">
-        <v>0.0428</v>
+        <v>0.0696</v>
       </c>
       <c r="G141" t="n">
-        <v>98.54000000000001</v>
+        <v>98.28</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>0093KA</t>
+          <t>0513KA</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>gender &gt; number</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4827,29 +4827,29 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4.0674</v>
+        <v>3.1533</v>
       </c>
       <c r="F142" t="n">
-        <v>1.2527</v>
+        <v>0.0244</v>
       </c>
       <c r="G142" t="n">
-        <v>69.2</v>
+        <v>99.23</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>0095AKA</t>
+          <t>0516KA</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Gender Nouns &gt; Gender ProN</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4858,29 +4858,29 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>3.5859</v>
+        <v>2.4602</v>
       </c>
       <c r="F143" t="n">
-        <v>0.0309</v>
+        <v>0.0376</v>
       </c>
       <c r="G143" t="n">
-        <v>99.14</v>
+        <v>98.47</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>0095BKA</t>
+          <t>0521KA</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Adj agree noun &gt; Dem agree noun</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4889,29 +4889,29 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3.9912</v>
+        <v>1.7738</v>
       </c>
       <c r="F144" t="n">
-        <v>0.022</v>
+        <v>0.0611</v>
       </c>
       <c r="G144" t="n">
-        <v>99.45</v>
+        <v>96.56</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>0107BKA</t>
+          <t>0564KA</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Du (noun) &gt; Du (pronoun)</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4920,29 +4920,29 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5.3293</v>
+        <v>2.4277</v>
       </c>
       <c r="F145" t="n">
-        <v>0.0179</v>
+        <v>0.1867</v>
       </c>
       <c r="G145" t="n">
-        <v>99.66</v>
+        <v>92.31</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>0110KA</t>
+          <t>0577KA</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>suppl noun &gt; suppl pron|verb</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4951,29 +4951,29 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>3.3336</v>
+        <v>2.1474</v>
       </c>
       <c r="F146" t="n">
-        <v>0.032</v>
+        <v>0.0418</v>
       </c>
       <c r="G146" t="n">
-        <v>99.04000000000001</v>
+        <v>98.05</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>0125KA</t>
+          <t>0612KA</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>switch-reference marking &gt; V-final</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4982,29 +4982,29 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>2.3959</v>
+        <v>2.4176</v>
       </c>
       <c r="F147" t="n">
-        <v>0.0256</v>
+        <v>0.0252</v>
       </c>
       <c r="G147" t="n">
-        <v>98.93000000000001</v>
+        <v>98.95999999999999</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>0126NKA</t>
+          <t>0822KA</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>correlative Rel &gt; V-final;</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -5013,29 +5013,29 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4.6235</v>
+        <v>1.3651</v>
       </c>
       <c r="F148" t="n">
-        <v>0.033</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G148" t="n">
-        <v>99.29000000000001</v>
+        <v>94.95</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>0144KA</t>
+          <t>0917BKA</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>OV &gt; Gen-N</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5044,29 +5044,29 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2.4806</v>
+        <v>5.2069</v>
       </c>
       <c r="F149" t="n">
-        <v>0.0437</v>
+        <v>0.0267</v>
       </c>
       <c r="G149" t="n">
-        <v>98.23999999999999</v>
+        <v>99.48999999999999</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>0145KA</t>
+          <t>0982KA</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>locative comparative &gt; SOV | VSO</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5075,29 +5075,29 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5.1389</v>
+        <v>2.4174</v>
       </c>
       <c r="F150" t="n">
-        <v>0.0193</v>
+        <v>0.0558</v>
       </c>
       <c r="G150" t="n">
-        <v>99.63</v>
+        <v>97.69</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>0179CKA</t>
+          <t>1027AKA</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>VO -&gt; no morph tense | no  case</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -5106,29 +5106,29 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2.7192</v>
+        <v>4.9982</v>
       </c>
       <c r="F151" t="n">
-        <v>9.101000000000001</v>
+        <v>0.0195</v>
       </c>
       <c r="G151" t="n">
-        <v>-234.7</v>
+        <v>99.61</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>0232KA</t>
+          <t>1027BKA</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>no morph tense -&gt; no case|VO</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5137,29 +5137,29 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2.9543</v>
+        <v>3.1951</v>
       </c>
       <c r="F152" t="n">
-        <v>0.0693</v>
+        <v>0.033</v>
       </c>
       <c r="G152" t="n">
-        <v>97.66</v>
+        <v>98.97</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>0238AKA</t>
+          <t>1027CKA</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>no case &gt; no morph tense | VO</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5168,29 +5168,29 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1.7623</v>
+        <v>3.1826</v>
       </c>
       <c r="F153" t="n">
-        <v>0.038</v>
+        <v>0.0338</v>
       </c>
       <c r="G153" t="n">
-        <v>97.84</v>
+        <v>98.94</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>0238BKA</t>
+          <t>1053KA</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>agreement determiners &gt; agreement modifiers</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5199,29 +5199,29 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1.9534</v>
+        <v>1.745</v>
       </c>
       <c r="F154" t="n">
-        <v>0.0577</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="G154" t="n">
-        <v>97.05</v>
+        <v>96.15000000000001</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>0320KA</t>
+          <t>1114KA</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>VO &gt; Comp-S</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5230,29 +5230,29 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>3.0338</v>
+        <v>4.5168</v>
       </c>
       <c r="F155" t="n">
-        <v>0.0341</v>
+        <v>0.016</v>
       </c>
       <c r="G155" t="n">
-        <v>98.88</v>
+        <v>99.65000000000001</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>0331AKA</t>
+          <t>1152KA</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Rel-N &gt; N-Rel</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5261,29 +5261,29 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4.5275</v>
+        <v>2.5423</v>
       </c>
       <c r="F156" t="n">
-        <v>0.0513</v>
+        <v>0.0439</v>
       </c>
       <c r="G156" t="n">
-        <v>98.87</v>
+        <v>98.27</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>0344KA</t>
+          <t>1163KA</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>indefinite article &gt; definite article</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5292,29 +5292,29 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>3.5075</v>
+        <v>1.2682</v>
       </c>
       <c r="F157" t="n">
-        <v>0.8973</v>
+        <v>0.0613</v>
       </c>
       <c r="G157" t="n">
-        <v>74.42</v>
+        <v>95.17</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>0357KA</t>
+          <t>1267BKA</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>SVO &gt; not ergative</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5323,29 +5323,29 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1.2733</v>
+        <v>4.5319</v>
       </c>
       <c r="F158" t="n">
-        <v>0.9765</v>
+        <v>0.0459</v>
       </c>
       <c r="G158" t="n">
-        <v>23.31</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>0454KA</t>
+          <t>1341KA</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>verbal reciprocal/reflexive &gt; verb agreement with subject</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5354,29 +5354,29 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>3.5663</v>
+        <v>3.1597</v>
       </c>
       <c r="F159" t="n">
-        <v>0.0343</v>
+        <v>0.0416</v>
       </c>
       <c r="G159" t="n">
-        <v>99.04000000000001</v>
+        <v>98.68000000000001</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>0489KA</t>
+          <t>1415KA</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>poss agree &gt; verbal agree S</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -5385,29 +5385,29 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4.2541</v>
+        <v>3.471</v>
       </c>
       <c r="F160" t="n">
-        <v>0.0195</v>
+        <v>0.0403</v>
       </c>
       <c r="G160" t="n">
-        <v>99.54000000000001</v>
+        <v>98.84</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>0493AKA</t>
+          <t>1431MKA</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>less case &gt; more tense</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5416,29 +5416,29 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1.9978</v>
+        <v>2.9014</v>
       </c>
       <c r="F161" t="n">
-        <v>0.0621</v>
+        <v>0.0441</v>
       </c>
       <c r="G161" t="n">
-        <v>96.89</v>
+        <v>98.48</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>0511AKA</t>
+          <t>1431NKA</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>more case &gt; less tense</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -5447,29 +5447,29 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.9302</v>
+        <v>3.067</v>
       </c>
       <c r="F162" t="n">
-        <v>0.6424</v>
+        <v>0.0297</v>
       </c>
       <c r="G162" t="n">
-        <v>30.93</v>
+        <v>99.03</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>0511BKA</t>
+          <t>1550KA</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>V-initial &gt; N-Rel</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -5478,29 +5478,29 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4.0338</v>
+        <v>5.7749</v>
       </c>
       <c r="F163" t="n">
-        <v>0.0696</v>
+        <v>0.1905</v>
       </c>
       <c r="G163" t="n">
-        <v>98.28</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>0513KA</t>
+          <t>1586KA</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>poss head-marked &gt; opp alien-inalien poss</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5509,29 +5509,29 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>3.1533</v>
+        <v>3.5375</v>
       </c>
       <c r="F164" t="n">
-        <v>0.0244</v>
+        <v>0.0325</v>
       </c>
       <c r="G164" t="n">
-        <v>99.23</v>
+        <v>99.08</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>0516KA</t>
+          <t>1591KA</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>internal relative clause &gt; SOV</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -5540,29 +5540,29 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>2.4602</v>
+        <v>1.1324</v>
       </c>
       <c r="F165" t="n">
-        <v>0.0376</v>
+        <v>0.101</v>
       </c>
       <c r="G165" t="n">
-        <v>98.47</v>
+        <v>91.08</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>0517KA</t>
+          <t>1611KA</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>verb-patient agreement &gt; verb-agent agreement</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -5571,29 +5571,29 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1.1899</v>
+        <v>3.5488</v>
       </c>
       <c r="F166" t="n">
-        <v>0.9502</v>
+        <v>0.025</v>
       </c>
       <c r="G166" t="n">
-        <v>20.14</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>0521KA</t>
+          <t>1612CKA</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>SOV &amp; N-Num &gt; N-Num agr</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -5602,29 +5602,29 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1.7738</v>
+        <v>4.4998</v>
       </c>
       <c r="F167" t="n">
-        <v>0.0611</v>
+        <v>0.8339</v>
       </c>
       <c r="G167" t="n">
-        <v>96.56</v>
+        <v>81.47</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>0564KA</t>
+          <t>1667AKA</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>S-Comp &gt; SOV</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -5633,29 +5633,29 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>2.4277</v>
+        <v>0.8995</v>
       </c>
       <c r="F168" t="n">
-        <v>0.1867</v>
+        <v>0.0638</v>
       </c>
       <c r="G168" t="n">
-        <v>92.31</v>
+        <v>92.91</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>0572KA</t>
+          <t>1741KA</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Gen prefix &gt; verbal prefixes</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -5664,29 +5664,29 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>2.2296</v>
+        <v>3.1169</v>
       </c>
       <c r="F169" t="n">
-        <v>0.0592</v>
+        <v>0.036</v>
       </c>
       <c r="G169" t="n">
-        <v>97.34999999999999</v>
+        <v>98.84</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>0798KA</t>
+          <t>1994DKA</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>non-affixed Gen-N &gt; Adj-N</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Cross-Framework Consensus</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5695,695 +5695,695 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>2.7204</v>
+        <v>3.5193</v>
       </c>
       <c r="F170" t="n">
-        <v>0.0649</v>
+        <v>0.0315</v>
       </c>
       <c r="G170" t="n">
-        <v>97.61</v>
+        <v>99.11</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>0837KA</t>
+          <t>0056KA</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>VSO &gt; N-Adj</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Isolate-Driven False Positives</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Significant (Both)</t>
+          <t>Non-Significant</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5.6176</v>
+        <v>3.592</v>
       </c>
       <c r="F171" t="n">
-        <v>0.304</v>
+        <v>2.6432</v>
       </c>
       <c r="G171" t="n">
-        <v>94.59</v>
+        <v>26.41</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1027CKA</t>
+          <t>0245AKA</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>free order &gt; inflection nouns</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Isolate-Driven False Positives</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Significant (Both)</t>
+          <t>Non-Significant</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>3.1826</v>
+        <v>1.894</v>
       </c>
       <c r="F172" t="n">
-        <v>0.0338</v>
+        <v>0.06</v>
       </c>
       <c r="G172" t="n">
-        <v>98.94</v>
+        <v>96.83</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1028AKA</t>
+          <t>0517KA</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>gender (1) &gt; gender (2 &amp;| 3)</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Isolate-Driven False Positives</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Significant (Both)</t>
+          <t>Non-Significant</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5.4887</v>
+        <v>1.1899</v>
       </c>
       <c r="F173" t="n">
-        <v>0.0226</v>
+        <v>0.9502</v>
       </c>
       <c r="G173" t="n">
-        <v>99.59</v>
+        <v>20.14</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1028CKA</t>
+          <t>1545KA</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>V-initial &gt; N-Dem-Num-Adj</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Isolate-Driven False Positives</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Significant (Both)</t>
+          <t>Non-Significant</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>3.5756</v>
+        <v>5.7574</v>
       </c>
       <c r="F174" t="n">
-        <v>0.0278</v>
+        <v>0.23</v>
       </c>
       <c r="G174" t="n">
-        <v>99.22</v>
+        <v>96</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1111KA</t>
+          <t>1592KA</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>internal relative clause &gt; left-branching NP structure</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Isolate-Driven False Positives</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Significant (Both)</t>
+          <t>Non-Significant</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>3.0269</v>
+        <v>1.3654</v>
       </c>
       <c r="F175" t="n">
-        <v>0.0285</v>
+        <v>0.0452</v>
       </c>
       <c r="G175" t="n">
-        <v>99.06</v>
+        <v>96.69</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1142BKA</t>
+          <t>1994BKA</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>non-affixed Gen-N &gt; OV</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Isolate-Driven False Positives</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Significant (Both)</t>
+          <t>Non-Significant</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>3.6674</v>
+        <v>3.6273</v>
       </c>
       <c r="F176" t="n">
-        <v>0.0243</v>
+        <v>0.031</v>
       </c>
       <c r="G176" t="n">
-        <v>99.34</v>
+        <v>99.14</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1267AKA</t>
+          <t>0001_OR_2BKA</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>N-Adp &gt; Gen-N</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Rescued Universals (3D Bounded)</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Significant (Both)</t>
+          <t>Significant (3D Only)</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>4.4536</v>
+        <v>3.3722</v>
       </c>
       <c r="F177" t="n">
-        <v>0.0726</v>
+        <v>0.0455</v>
       </c>
       <c r="G177" t="n">
-        <v>98.37</v>
+        <v>98.65000000000001</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1267BKA</t>
+          <t>0008KA</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>SOV|OSV &gt; case</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Rescued Universals (3D Bounded)</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Significant (Both)</t>
+          <t>Significant (3D Only)</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>4.5319</v>
+        <v>5.1106</v>
       </c>
       <c r="F178" t="n">
-        <v>0.0459</v>
+        <v>0.0189</v>
       </c>
       <c r="G178" t="n">
-        <v>98.98999999999999</v>
+        <v>99.63</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1341KA</t>
+          <t>0088KA</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>N-Dem &gt; N-Rel</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Rescued Universals (3D Bounded)</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Significant (Both)</t>
+          <t>Significant (3D Only)</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>3.1597</v>
+        <v>2.9352</v>
       </c>
       <c r="F179" t="n">
-        <v>0.0416</v>
+        <v>0.0428</v>
       </c>
       <c r="G179" t="n">
-        <v>98.68000000000001</v>
+        <v>98.54000000000001</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1349KA</t>
+          <t>0095BKA</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>N-Adp &amp; (Adj-N | Rel-N) &gt; Num-N</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Rescued Universals (3D Bounded)</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Significant (Both)</t>
+          <t>Significant (3D Only)</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>4.8004</v>
+        <v>3.9912</v>
       </c>
       <c r="F180" t="n">
-        <v>0.0137</v>
+        <v>0.022</v>
       </c>
       <c r="G180" t="n">
-        <v>99.70999999999999</v>
+        <v>99.45</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1434KA</t>
+          <t>0116KA</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>case &gt; number</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Rescued Universals (3D Bounded)</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Significant (Both)</t>
+          <t>Significant (3D Only)</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>2.3668</v>
+        <v>2.3053</v>
       </c>
       <c r="F181" t="n">
-        <v>0.0538</v>
+        <v>0.0473</v>
       </c>
       <c r="G181" t="n">
-        <v>97.73</v>
+        <v>97.95</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1436KA</t>
+          <t>0121KA</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Adp-N &amp; N-Num &gt; N-Rel</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Rescued Universals (3D Bounded)</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Significant (Both)</t>
+          <t>Significant (3D Only)</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>4.0214</v>
+        <v>4.3015</v>
       </c>
       <c r="F182" t="n">
-        <v>0.0373</v>
+        <v>0.3778</v>
       </c>
       <c r="G182" t="n">
-        <v>99.06999999999999</v>
+        <v>91.22</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1548AKA</t>
+          <t>0174KA</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>Adp-N &amp; N-Num &gt; N-Gen</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Rescued Universals (3D Bounded)</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Significant (Both)</t>
+          <t>Significant (3D Only)</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5.2734</v>
+        <v>4.0499</v>
       </c>
       <c r="F183" t="n">
-        <v>0.0136</v>
+        <v>0.3563</v>
       </c>
       <c r="G183" t="n">
-        <v>99.73999999999999</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1548BKA</t>
+          <t>0230AKA</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>rigid order &gt; no case</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Rescued Universals (3D Bounded)</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Significant (Both)</t>
+          <t>Significant (3D Only)</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6.1999</v>
+        <v>2.0356</v>
       </c>
       <c r="F184" t="n">
-        <v>0.6281</v>
+        <v>0.1214</v>
       </c>
       <c r="G184" t="n">
-        <v>89.87</v>
+        <v>94.04000000000001</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1549KA</t>
+          <t>0230DKA</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>free order &gt; case</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Rescued Universals (3D Bounded)</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Significant (Both)</t>
+          <t>Significant (3D Only)</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5.6407</v>
+        <v>2.0464</v>
       </c>
       <c r="F185" t="n">
-        <v>0.4412</v>
+        <v>0.1251</v>
       </c>
       <c r="G185" t="n">
-        <v>92.18000000000001</v>
+        <v>93.89</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1550KA</t>
+          <t>0507KA</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>(person)-number (verb) &gt; tense-mood (verb)</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Rescued Universals (3D Bounded)</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Significant (Both)</t>
+          <t>Significant (3D Only)</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>5.7749</v>
+        <v>3.6421</v>
       </c>
       <c r="F186" t="n">
-        <v>0.1905</v>
+        <v>0.0328</v>
       </c>
       <c r="G186" t="n">
-        <v>96.7</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1612AKA</t>
+          <t>0582KA</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>inflection (noun) &gt; inflection (pronoun)</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Rescued Universals (3D Bounded)</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Significant (Both)</t>
+          <t>Significant (3D Only)</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1.6023</v>
+        <v>2.6821</v>
       </c>
       <c r="F187" t="n">
-        <v>1.2223</v>
+        <v>0.0517</v>
       </c>
       <c r="G187" t="n">
-        <v>23.71</v>
+        <v>98.06999999999999</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1612BKA</t>
+          <t>1267AKA</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>ergative &gt; VSO | SOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Rescued Universals (3D Bounded)</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Significant (Both)</t>
+          <t>Significant (3D Only)</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>4.1805</v>
+        <v>4.4536</v>
       </c>
       <c r="F188" t="n">
-        <v>0.2677</v>
+        <v>0.0726</v>
       </c>
       <c r="G188" t="n">
-        <v>93.59999999999999</v>
+        <v>98.37</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1653KA</t>
+          <t>1427KA</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>no prefix &gt; infl local cases</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Rescued Universals (3D Bounded)</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Significant (Both)</t>
+          <t>Significant (3D Only)</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>3.4836</v>
+        <v>4.0676</v>
       </c>
       <c r="F189" t="n">
-        <v>0.0252</v>
+        <v>1.5818</v>
       </c>
       <c r="G189" t="n">
-        <v>99.28</v>
+        <v>61.11</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1667AKA</t>
+          <t>1544KA</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>V-initial &gt; verbal case-marking</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Rescued Universals (3D Bounded)</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Significant (Both)</t>
+          <t>Significant (3D Only)</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>0.8995</v>
+        <v>5.8409</v>
       </c>
       <c r="F190" t="n">
-        <v>0.0638</v>
+        <v>0.1836</v>
       </c>
       <c r="G190" t="n">
-        <v>92.91</v>
+        <v>96.86</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1827KA</t>
+          <t>1612DKA</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>SOV &amp; N-Dem &gt; N-Dem agr</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Rescued Universals (3D Bounded)</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Significant (Both)</t>
+          <t>Significant (3D Only)</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>2.9949</v>
+        <v>3.332</v>
       </c>
       <c r="F191" t="n">
-        <v>0.0303</v>
+        <v>0.1745</v>
       </c>
       <c r="G191" t="n">
-        <v>98.98999999999999</v>
+        <v>94.76000000000001</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1994BKA</t>
+          <t>1994AKA</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Supplementary Typological Trait Invariant</t>
+          <t>non-affixed Gen-N &gt; N-Adp</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Stable Core Consensus</t>
+          <t>Rescued Universals (3D Bounded)</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Significant (Both)</t>
+          <t>Significant (3D Only)</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>3.6273</v>
+        <v>3.6364</v>
       </c>
       <c r="F192" t="n">
-        <v>0.031</v>
+        <v>0.0266</v>
       </c>
       <c r="G192" t="n">
-        <v>99.14</v>
+        <v>99.27</v>
       </c>
     </row>
   </sheetData>
